--- a/远征S25/S25.xlsx
+++ b/远征S25/S25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\utility\naruto\远征S25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C71E58-58AD-413C-A70E-CC42D9EE78CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34C0D74-A276-4657-A82A-917D0977CABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1139,6 +1139,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1247,13 +1248,222 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="31">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDB75FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor rgb="FFFF8585"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="lightGrid">
+          <fgColor theme="8" tint="-0.24994659260841701"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="8" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="gray0625">
+          <fgColor theme="8" tint="-0.24994659260841701"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFF00"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9900CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14993743705557422"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1374,16 +1584,16 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="30"/>
+      <tableStyleElement type="totalRow" dxfId="29"/>
+      <tableStyleElement type="firstRowStripe" dxfId="28"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="27"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="26"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="25"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="24"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="23"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="22"/>
+      <tableStyleElement type="pageFieldValues" dxfId="21"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -1686,166 +1896,166 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:57" ht="28.35" customHeight="1">
-      <c r="A1" s="108">
+      <c r="A1" s="109">
         <f ca="1">(_xlfn.DAYS(TODAY(),A4)+2)/((_xlfn.DAYS(A93,A4))+1)</f>
-        <v>-1.1111111111111112E-2</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="111" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
-      <c r="Z1" s="112"/>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="112"/>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="112"/>
-      <c r="AF1" s="112"/>
-      <c r="AG1" s="113"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="112" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="113"/>
+      <c r="P1" s="113"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="113"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="113"/>
+      <c r="U1" s="113"/>
+      <c r="V1" s="113"/>
+      <c r="W1" s="113"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="113"/>
+      <c r="Z1" s="113"/>
+      <c r="AA1" s="113"/>
+      <c r="AB1" s="113"/>
+      <c r="AC1" s="113"/>
+      <c r="AD1" s="113"/>
+      <c r="AE1" s="113"/>
+      <c r="AF1" s="113"/>
+      <c r="AG1" s="114"/>
       <c r="AH1" s="19"/>
       <c r="AI1" s="19"/>
       <c r="AJ1" s="19"/>
-      <c r="AO1" s="106"/>
-      <c r="AP1" s="106"/>
-      <c r="AQ1" s="106"/>
+      <c r="AO1" s="107"/>
+      <c r="AP1" s="107"/>
+      <c r="AQ1" s="107"/>
       <c r="AR1" s="20"/>
     </row>
     <row r="2" spans="1:57" ht="16.350000000000001" customHeight="1">
       <c r="B2" s="21"/>
       <c r="C2" s="22"/>
-      <c r="D2" s="114" t="s">
+      <c r="D2" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="115"/>
-      <c r="F2" s="116">
+      <c r="E2" s="116"/>
+      <c r="F2" s="117">
         <f>SUM(F4:F93)+SUM(H4:H93)</f>
-        <v>7000</v>
-      </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="118" t="s">
+        <v>15505</v>
+      </c>
+      <c r="G2" s="117"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="119"/>
+      <c r="J2" s="120"/>
       <c r="K2" s="23" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="23">
         <f>COUNTIF(I4:P93,"&lt;&gt;空")</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="119" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="120"/>
-      <c r="Q2" s="121" t="s">
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="122"/>
+      <c r="R2" s="123"/>
       <c r="S2" s="24" t="s">
         <v>3</v>
       </c>
       <c r="T2" s="24">
         <f>COUNTIF(Q4:X93,"&lt;&gt;空")</f>
-        <v>0</v>
-      </c>
-      <c r="U2" s="122" t="s">
+        <v>66</v>
+      </c>
+      <c r="U2" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="123"/>
-      <c r="Y2" s="124" t="s">
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="124"/>
+      <c r="Y2" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="125"/>
+      <c r="Z2" s="126"/>
       <c r="AA2" s="26" t="s">
         <v>7</v>
       </c>
       <c r="AB2" s="25">
         <f>COUNTIF(Y4:AF93,"&lt;&gt;空")</f>
-        <v>0</v>
-      </c>
-      <c r="AC2" s="125" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC2" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="AD2" s="125"/>
-      <c r="AE2" s="125"/>
-      <c r="AF2" s="126"/>
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="127"/>
       <c r="AG2" s="27">
         <f t="shared" ref="AG2:AJ2" si="0">SUM(AG4:AG93)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AH2" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AI2" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AK2" s="103" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="AO2" s="107"/>
-      <c r="AP2" s="107"/>
-      <c r="AQ2" s="107"/>
+      <c r="AO2" s="108"/>
+      <c r="AP2" s="108"/>
+      <c r="AQ2" s="108"/>
       <c r="AR2" s="20"/>
       <c r="AU2" t="s">
         <v>9</v>
       </c>
       <c r="AV2">
         <f>SUM(AV4:AV29)</f>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AW2" t="s">
         <v>10</v>
       </c>
       <c r="AX2">
         <f>AR47</f>
-        <v>10800</v>
+        <v>1882</v>
       </c>
       <c r="AY2" t="s">
         <v>11</v>
       </c>
       <c r="AZ2">
         <f>SUM(AX4:AZ29)+7000</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="BA2" s="29"/>
       <c r="BB2" s="30" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="31.5" customHeight="1">
+    <row r="3" spans="1:57" ht="31.5" customHeight="1" thickBot="1">
       <c r="A3" s="31" t="s">
         <v>13</v>
       </c>
@@ -1954,7 +2164,7 @@
       <c r="AJ3" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="AK3" s="104"/>
+      <c r="AK3" s="105"/>
       <c r="AL3" s="46" t="s">
         <v>24</v>
       </c>
@@ -2008,7 +2218,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:57" s="18" customFormat="1">
+    <row r="4" spans="1:57" s="18" customFormat="1" ht="15.75" thickBot="1">
       <c r="A4" s="95">
         <v>46276</v>
       </c>
@@ -2020,40 +2230,40 @@
       </c>
       <c r="D4" s="55">
         <f>(SUM(粮草!A4:X4)+AG4*10*IF(AK4="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="E4" s="57">
         <f>SUM($B$4:B4)+SUM($C$4:C4)-SUM($D$4:D4)</f>
-        <v>6800</v>
+        <v>4360</v>
       </c>
       <c r="F4" s="55">
         <f>SUM(经验!A4:X4)</f>
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="G4" s="55">
         <f>SUM($F$4:F4)+SUM($H$4:H4)</f>
-        <v>500</v>
+        <v>1010</v>
       </c>
       <c r="H4" s="55">
         <v>500</v>
       </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" t="s">
-        <v>41</v>
+      <c r="I4" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" s="58" t="s">
+        <v>39</v>
       </c>
       <c r="O4" s="60" t="s">
         <v>41</v>
@@ -2061,23 +2271,23 @@
       <c r="P4" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" t="s">
-        <v>41</v>
-      </c>
-      <c r="V4" t="s">
-        <v>41</v>
+      <c r="Q4" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="S4" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="73" t="s">
+        <v>51</v>
       </c>
       <c r="W4" s="60" t="s">
         <v>41</v>
@@ -2111,9 +2321,11 @@
       </c>
       <c r="AG4" s="62">
         <f>AH4+AI4+AJ4</f>
-        <v>0</v>
-      </c>
-      <c r="AH4" s="62"/>
+        <v>46</v>
+      </c>
+      <c r="AH4" s="62">
+        <v>46</v>
+      </c>
       <c r="AI4" s="62"/>
       <c r="AJ4" s="62"/>
       <c r="AK4" s="63" t="s">
@@ -2121,11 +2333,11 @@
       </c>
       <c r="AL4" s="64">
         <f>6-COUNTIF(I4:P4,"&lt;&gt;空")+COUNTIF(I4:P4,"塔1")*5</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM4" s="64">
         <f>6-COUNTIF(Q4:X4,"&lt;&gt;空")+COUNTIF(Q4:X4,"塔1")*5</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="64">
         <f>6-COUNTIF(Y4:AF4,"&lt;&gt;空")+COUNTIF(Y4:AF4,"塔1")*5</f>
@@ -2145,11 +2357,11 @@
       </c>
       <c r="AS4" s="65">
         <f>COUNTIF($I$4:$P93,AO4)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT4" s="65">
         <f>COUNTIF($Q$4:$X$93,AO4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU4" s="65">
         <f>COUNTIF($Y$4:$AF$93,AO4)</f>
@@ -2157,18 +2369,18 @@
       </c>
       <c r="AV4" s="66">
         <f>AS4+AT4+AU4</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW4" s="67">
         <v>16</v>
       </c>
       <c r="AX4" s="67">
         <f t="shared" ref="AX4:AX29" si="1">AS4*$AQ4</f>
-        <v>0</v>
+        <v>665</v>
       </c>
       <c r="AY4" s="67">
         <f t="shared" ref="AY4:AZ19" si="2">AT4*$AQ4</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AZ4" s="67">
         <f t="shared" si="2"/>
@@ -2182,7 +2394,7 @@
       </c>
       <c r="BD4" s="67">
         <f>AR4*AV4</f>
-        <v>0</v>
+        <v>1017.1085160268606</v>
       </c>
     </row>
     <row r="5" spans="1:57" s="18" customFormat="1">
@@ -2195,40 +2407,40 @@
       <c r="C5" s="56"/>
       <c r="D5" s="55">
         <f>(SUM(粮草!A5:X5)+AG5*10*IF(AK5="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E5" s="57">
         <f>SUM($B$4:B5)+SUM($C$4:C5)-SUM($D$4:D5)</f>
-        <v>8400</v>
+        <v>3980</v>
       </c>
       <c r="F5" s="55">
         <f>SUM(经验!A5:X5)</f>
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="G5" s="55">
         <f>SUM($F$4:F5)+SUM($H$4:H5)</f>
-        <v>500</v>
+        <v>1520</v>
       </c>
       <c r="H5" s="55">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s">
-        <v>41</v>
+      <c r="I5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="58" t="s">
+        <v>39</v>
       </c>
       <c r="O5" s="60" t="s">
         <v>41</v>
@@ -2236,23 +2448,23 @@
       <c r="P5" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" t="s">
-        <v>41</v>
+      <c r="Q5" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="R5" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="S5" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="T5" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="V5" s="73" t="s">
+        <v>51</v>
       </c>
       <c r="W5" s="60" t="s">
         <v>41</v>
@@ -2296,11 +2508,11 @@
       </c>
       <c r="AL5" s="64">
         <f>MIN(AL4+6,18)-COUNTIF(I5:P5,"&lt;&gt;空")+COUNTIF(I5:P5,"历练")+COUNTIF(I5:P5,"营地")*2+COUNTIF(I5:P5,"塔1")*5</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AM5" s="64">
         <f>MIN(AM4+6,18)-COUNTIF(Q5:X5,"&lt;&gt;空")+COUNTIF(Q5:X5,"历练")+COUNTIF(Q5:X5,"营地")*2+COUNTIF(Q5:X5,"塔1")*5</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="64">
         <f>MIN(AN4+6,18)-COUNTIF(Y5:AF5,"&lt;&gt;空")+COUNTIF(Y5:AF5,"历练")+COUNTIF(Y5:AF5,"营地")*2+COUNTIF(Y5:AF5,"塔1")*5</f>
@@ -2324,15 +2536,15 @@
       </c>
       <c r="AT5" s="65">
         <f t="shared" ref="AT5:AT29" si="4">COUNTIF($Q$4:$X$93,AO5)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU5" s="65">
         <f t="shared" ref="AU5:AU29" si="5">COUNTIF($Y$4:$AF$93,AO5)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV5" s="66">
         <f t="shared" ref="AV5:AV26" si="6">AS5+AT5+AU5</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AW5" s="67">
         <v>28</v>
@@ -2343,19 +2555,19 @@
       </c>
       <c r="AY5" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AZ5" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BA5" s="105" t="s">
+        <v>160</v>
+      </c>
+      <c r="BA5" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="BB5" s="105"/>
+      <c r="BB5" s="106"/>
       <c r="BD5" s="67">
         <f t="shared" ref="BD5:BD29" si="7">AR5*AV5</f>
-        <v>0</v>
+        <v>234.66589297695242</v>
       </c>
     </row>
     <row r="6" spans="1:57" s="18" customFormat="1">
@@ -2368,40 +2580,40 @@
       <c r="C6" s="56"/>
       <c r="D6" s="55">
         <f>(SUM(粮草!A6:X6)+AG6*10*IF(AK6="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="E6" s="57">
         <f>SUM($B$4:B6)+SUM($C$4:C6)-SUM($D$4:D6)</f>
-        <v>10000</v>
+        <v>3840</v>
       </c>
       <c r="F6" s="55">
         <f>SUM(经验!A6:X6)</f>
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="G6" s="55">
         <f>SUM($F$4:F6)+SUM($H$4:H6)</f>
-        <v>500</v>
+        <v>1960</v>
       </c>
       <c r="H6" s="55">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" t="s">
-        <v>41</v>
+      <c r="I6" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="58" t="s">
+        <v>39</v>
       </c>
       <c r="O6" s="60" t="s">
         <v>41</v>
@@ -2409,20 +2621,20 @@
       <c r="P6" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" t="s">
-        <v>41</v>
-      </c>
-      <c r="S6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T6" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6" t="s">
-        <v>41</v>
+      <c r="Q6" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="T6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>58</v>
       </c>
       <c r="V6" t="s">
         <v>41</v>
@@ -2469,11 +2681,11 @@
       </c>
       <c r="AL6" s="64">
         <f t="shared" ref="AL6:AL69" si="8">MIN(AL5+6,18)-COUNTIF(I6:P6,"&lt;&gt;空")+COUNTIF(I6:P6,"历练")+COUNTIF(I6:P6,"营地")*2+COUNTIF(I6:P6,"塔1")*5</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AM6" s="64">
         <f t="shared" ref="AM6:AM69" si="9">MIN(AM5+6,18)-COUNTIF(Q6:X6,"&lt;&gt;空")+COUNTIF(Q6:X6,"历练")+COUNTIF(Q6:X6,"营地")*2+COUNTIF(Q6:X6,"塔1")*5</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AN6" s="64">
         <f t="shared" ref="AN6:AN30" si="10">MIN(AN5+6,18)-COUNTIF(Y6:AF6,"&lt;&gt;空")+COUNTIF(Y6:AF6,"历练")+COUNTIF(Y6:AF6,"营地")*2+COUNTIF(Y6:AF6,"塔1")*5</f>
@@ -2493,40 +2705,40 @@
       </c>
       <c r="AS6" s="65">
         <f>COUNTIF($I$4:$P95,AO6)</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT6" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU6" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV6" s="66">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AW6" s="67">
         <v>54</v>
       </c>
       <c r="AX6" s="67">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="AY6" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="AZ6" s="67">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BA6" s="106"/>
-      <c r="BB6" s="106"/>
+        <v>315</v>
+      </c>
+      <c r="BA6" s="107"/>
+      <c r="BB6" s="107"/>
       <c r="BD6" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="7" spans="1:57">
@@ -2539,70 +2751,70 @@
       <c r="C7" s="67"/>
       <c r="D7" s="55">
         <f>(SUM(粮草!A7:X7)+AG7*10*IF(AK7="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2370</v>
       </c>
       <c r="E7" s="57">
         <f>SUM($B$4:B7)+SUM($C$4:C7)-SUM($D$4:D7)</f>
-        <v>11600</v>
+        <v>3070</v>
       </c>
       <c r="F7" s="55">
         <f>SUM(经验!A7:X7)</f>
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="G7" s="55">
         <f>SUM($F$4:F7)+SUM($H$4:H7)</f>
-        <v>700</v>
+        <v>2785</v>
       </c>
       <c r="H7" s="67">
         <v>200</v>
       </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="60" t="s">
-        <v>41</v>
+      <c r="I7" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="72" t="s">
+        <v>50</v>
       </c>
       <c r="P7" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Q7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" t="s">
-        <v>41</v>
-      </c>
-      <c r="S7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" t="s">
-        <v>41</v>
-      </c>
-      <c r="U7" t="s">
-        <v>41</v>
-      </c>
-      <c r="V7" t="s">
-        <v>41</v>
-      </c>
-      <c r="W7" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="X7" s="60" t="s">
-        <v>41</v>
+      <c r="Q7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="W7" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="X7" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="Y7" t="s">
         <v>41</v>
@@ -2640,11 +2852,11 @@
       </c>
       <c r="AL7" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="AM7" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="AN7" s="64">
         <f t="shared" si="10"/>
@@ -2668,7 +2880,7 @@
       </c>
       <c r="AT7" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU7" s="65">
         <f t="shared" si="5"/>
@@ -2676,7 +2888,7 @@
       </c>
       <c r="AV7" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW7">
         <v>22</v>
@@ -2687,17 +2899,17 @@
       </c>
       <c r="AY7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="AZ7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BA7" s="106"/>
-      <c r="BB7" s="106"/>
+      <c r="BA7" s="107"/>
+      <c r="BB7" s="107"/>
       <c r="BD7" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="BE7" s="18"/>
     </row>
@@ -2711,67 +2923,67 @@
       <c r="C8" s="67"/>
       <c r="D8" s="55">
         <f>(SUM(粮草!A8:X8)+AG8*10*IF(AK8="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1710</v>
       </c>
       <c r="E8" s="57">
         <f>SUM($B$4:B8)+SUM($C$4:C8)-SUM($D$4:D8)</f>
-        <v>13200</v>
+        <v>2960</v>
       </c>
       <c r="F8" s="55">
         <f>SUM(经验!A8:X8)</f>
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="G8" s="55">
         <f>SUM($F$4:F8)+SUM($H$4:H8)</f>
-        <v>1000</v>
+        <v>3655</v>
       </c>
       <c r="H8" s="67">
         <v>300</v>
       </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>41</v>
-      </c>
-      <c r="N8" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" t="s">
-        <v>41</v>
-      </c>
-      <c r="S8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V8" t="s">
-        <v>41</v>
-      </c>
-      <c r="W8" s="60" t="s">
-        <v>41</v>
+      <c r="I8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="S8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="T8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="U8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="V8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="W8" s="59" t="s">
+        <v>40</v>
       </c>
       <c r="X8" s="60" t="s">
         <v>41</v>
@@ -2812,11 +3024,11 @@
       </c>
       <c r="AL8" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="AM8" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="AN8" s="64">
         <f t="shared" si="10"/>
@@ -2865,8 +3077,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BA8" s="106"/>
-      <c r="BB8" s="106"/>
+      <c r="BA8" s="107"/>
+      <c r="BB8" s="107"/>
       <c r="BD8" s="67">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -2880,55 +3092,57 @@
       <c r="B9" s="67">
         <v>1600</v>
       </c>
-      <c r="C9" s="67"/>
+      <c r="C9" s="67">
+        <v>50</v>
+      </c>
       <c r="D9" s="55">
         <f>(SUM(粮草!A9:X9)+AG9*10*IF(AK9="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="E9" s="57">
         <f>SUM($B$4:B9)+SUM($C$4:C9)-SUM($D$4:D9)</f>
-        <v>14800</v>
+        <v>3750</v>
       </c>
       <c r="F9" s="55">
         <f>SUM(经验!A9:X9)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G9" s="55">
         <f>SUM($F$4:F9)+SUM($H$4:H9)</f>
-        <v>1000</v>
+        <v>4015</v>
       </c>
       <c r="H9" s="67">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" t="s">
-        <v>41</v>
+      <c r="I9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P9" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="71" t="s">
+        <v>49</v>
       </c>
       <c r="S9" t="s">
         <v>41</v>
@@ -2984,11 +3198,11 @@
       </c>
       <c r="AL9" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-5</v>
       </c>
       <c r="AM9" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="64">
         <f t="shared" si="10"/>
@@ -3053,55 +3267,55 @@
       <c r="C10" s="67"/>
       <c r="D10" s="55">
         <f>(SUM(粮草!A10:X10)+AG10*10*IF(AK10="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2110</v>
       </c>
       <c r="E10" s="57">
         <f>SUM($B$4:B10)+SUM($C$4:C10)-SUM($D$4:D10)</f>
-        <v>16400</v>
+        <v>3240</v>
       </c>
       <c r="F10" s="55">
         <f>SUM(经验!A10:X10)</f>
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="G10" s="55">
         <f>SUM($F$4:F10)+SUM($H$4:H10)</f>
-        <v>1000</v>
+        <v>5275</v>
       </c>
       <c r="H10" s="67">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="N10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P10" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>41</v>
-      </c>
-      <c r="R10" t="s">
-        <v>41</v>
-      </c>
-      <c r="S10" t="s">
-        <v>41</v>
+      <c r="I10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q10" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="75" t="s">
+        <v>52</v>
+      </c>
+      <c r="S10" s="75" t="s">
+        <v>52</v>
       </c>
       <c r="T10" t="s">
         <v>41</v>
@@ -3154,11 +3368,11 @@
       </c>
       <c r="AL10" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-7</v>
       </c>
       <c r="AM10" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AN10" s="64">
         <f t="shared" si="10"/>
@@ -3182,7 +3396,7 @@
       </c>
       <c r="AT10" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU10" s="65">
         <f t="shared" si="5"/>
@@ -3190,7 +3404,7 @@
       </c>
       <c r="AV10" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10">
         <v>0</v>
@@ -3201,7 +3415,7 @@
       </c>
       <c r="AY10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AZ10">
         <f t="shared" si="2"/>
@@ -3209,7 +3423,7 @@
       </c>
       <c r="BD10" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="BE10" s="18"/>
     </row>
@@ -3223,61 +3437,61 @@
       <c r="C11" s="67"/>
       <c r="D11" s="55">
         <f>(SUM(粮草!A11:X11)+AG11*10*IF(AK11="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2210</v>
       </c>
       <c r="E11" s="57">
         <f>SUM($B$4:B11)+SUM($C$4:C11)-SUM($D$4:D11)</f>
-        <v>18000</v>
+        <v>2630</v>
       </c>
       <c r="F11" s="55">
         <f>SUM(经验!A11:X11)</f>
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="G11" s="55">
         <f>SUM($F$4:F11)+SUM($H$4:H11)</f>
-        <v>1000</v>
+        <v>5860</v>
       </c>
       <c r="H11" s="67">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P11" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>41</v>
-      </c>
-      <c r="R11" t="s">
-        <v>41</v>
-      </c>
-      <c r="S11" t="s">
-        <v>41</v>
-      </c>
-      <c r="T11" t="s">
-        <v>41</v>
-      </c>
-      <c r="U11" t="s">
-        <v>41</v>
+      <c r="I11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P11" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q11" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="R11" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="T11" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="U11" s="75" t="s">
+        <v>53</v>
       </c>
       <c r="V11" t="s">
         <v>41</v>
@@ -3319,16 +3533,16 @@
       <c r="AH11" s="62"/>
       <c r="AI11" s="62"/>
       <c r="AJ11" s="62"/>
-      <c r="AK11" s="80" t="s">
-        <v>57</v>
+      <c r="AK11" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="AL11" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="AM11" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AN11" s="64">
         <f t="shared" si="10"/>
@@ -3352,15 +3566,15 @@
       </c>
       <c r="AT11" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU11" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW11">
         <v>10</v>
@@ -3371,15 +3585,15 @@
       </c>
       <c r="AY11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AZ11">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD11" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>261.9988394654286</v>
       </c>
       <c r="BE11" s="18"/>
     </row>
@@ -3393,70 +3607,70 @@
       <c r="C12" s="67"/>
       <c r="D12" s="55">
         <f>(SUM(粮草!A12:X12)+AG12*10*IF(AK12="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2720</v>
       </c>
       <c r="E12" s="57">
         <f>SUM($B$4:B12)+SUM($C$4:C12)-SUM($D$4:D12)</f>
-        <v>19600</v>
+        <v>1510</v>
       </c>
       <c r="F12" s="55">
         <f>SUM(经验!A12:X12)</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G12" s="55">
         <f>SUM($F$4:F12)+SUM($H$4:H12)</f>
-        <v>1000</v>
+        <v>6580</v>
       </c>
       <c r="H12" s="67">
         <v>0</v>
       </c>
-      <c r="I12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>41</v>
-      </c>
-      <c r="R12" t="s">
-        <v>41</v>
-      </c>
-      <c r="S12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T12" t="s">
-        <v>41</v>
-      </c>
-      <c r="U12" t="s">
-        <v>41</v>
-      </c>
-      <c r="V12" t="s">
-        <v>41</v>
-      </c>
-      <c r="W12" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="X12" s="60" t="s">
-        <v>41</v>
+      <c r="I12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="R12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="T12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="U12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="V12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="W12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="X12" s="72" t="s">
+        <v>50</v>
       </c>
       <c r="Y12" t="s">
         <v>41</v>
@@ -3489,16 +3703,16 @@
       <c r="AH12" s="62"/>
       <c r="AI12" s="79"/>
       <c r="AJ12" s="62"/>
-      <c r="AK12" s="80" t="s">
-        <v>57</v>
+      <c r="AK12" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="AL12" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="AM12" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AN12" s="64">
         <f t="shared" si="10"/>
@@ -3522,7 +3736,7 @@
       </c>
       <c r="AT12" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" s="65">
         <f t="shared" si="5"/>
@@ -3530,7 +3744,7 @@
       </c>
       <c r="AV12" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12">
         <v>0</v>
@@ -3541,7 +3755,7 @@
       </c>
       <c r="AY12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AZ12">
         <f t="shared" si="2"/>
@@ -3549,7 +3763,7 @@
       </c>
       <c r="BD12" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>13.9998549331786</v>
       </c>
       <c r="BE12" s="18"/>
     </row>
@@ -3563,46 +3777,46 @@
       <c r="C13" s="67"/>
       <c r="D13" s="55">
         <f>(SUM(粮草!A13:X13)+AG13*10*IF(AK13="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1360</v>
       </c>
       <c r="E13" s="57">
         <f>SUM($B$4:B13)+SUM($C$4:C13)-SUM($D$4:D13)</f>
-        <v>21200</v>
+        <v>1750</v>
       </c>
       <c r="F13" s="55">
         <f>SUM(经验!A13:X13)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G13" s="55">
         <f>SUM($F$4:F13)+SUM($H$4:H13)</f>
-        <v>1000</v>
+        <v>6940</v>
       </c>
       <c r="H13" s="67">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J13" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" t="s">
-        <v>41</v>
-      </c>
-      <c r="M13" t="s">
-        <v>41</v>
-      </c>
-      <c r="N13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O13" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P13" s="60" t="s">
-        <v>41</v>
+      <c r="I13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13" s="72" t="s">
+        <v>50</v>
       </c>
       <c r="Q13" t="s">
         <v>41</v>
@@ -3659,16 +3873,16 @@
       <c r="AH13" s="79"/>
       <c r="AI13" s="79"/>
       <c r="AJ13" s="79"/>
-      <c r="AK13" s="80" t="s">
-        <v>57</v>
+      <c r="AK13" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="AL13" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-13</v>
       </c>
       <c r="AM13" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AN13" s="64">
         <f t="shared" si="10"/>
@@ -3731,46 +3945,46 @@
       <c r="C14" s="56"/>
       <c r="D14" s="55">
         <f>(SUM(粮草!A14:X14)+AG14*10*IF(AK14="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1360</v>
       </c>
       <c r="E14" s="57">
         <f>SUM($B$4:B14)+SUM($C$4:C14)-SUM($D$4:D14)</f>
-        <v>22800</v>
+        <v>1990</v>
       </c>
       <c r="F14" s="55">
         <f>SUM(经验!A14:X14)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G14" s="55">
         <f>SUM($F$4:F14)+SUM($H$4:H14)</f>
-        <v>1300</v>
+        <v>7600</v>
       </c>
       <c r="H14" s="55">
         <v>300</v>
       </c>
-      <c r="I14" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" t="s">
-        <v>41</v>
-      </c>
-      <c r="M14" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" t="s">
-        <v>41</v>
-      </c>
-      <c r="O14" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P14" s="60" t="s">
-        <v>41</v>
+      <c r="I14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O14" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" s="72" t="s">
+        <v>50</v>
       </c>
       <c r="Q14" t="s">
         <v>41</v>
@@ -3827,12 +4041,12 @@
       <c r="AH14" s="79"/>
       <c r="AI14" s="79"/>
       <c r="AJ14" s="79"/>
-      <c r="AK14" s="80" t="s">
-        <v>57</v>
+      <c r="AK14" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="AL14" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-15</v>
       </c>
       <c r="AM14" s="64">
         <f t="shared" si="9"/>
@@ -3899,46 +4113,46 @@
       <c r="C15" s="56"/>
       <c r="D15" s="55">
         <f>(SUM(粮草!A15:X15)+AG15*10*IF(AK15="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>1360</v>
       </c>
       <c r="E15" s="57">
         <f>SUM($B$4:B15)+SUM($C$4:C15)-SUM($D$4:D15)</f>
-        <v>24400</v>
+        <v>2230</v>
       </c>
       <c r="F15" s="55">
         <f>SUM(经验!A15:X15)</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G15" s="55">
         <f>SUM($F$4:F15)+SUM($H$4:H15)</f>
-        <v>1300</v>
+        <v>7960</v>
       </c>
       <c r="H15" s="55">
         <v>0</v>
       </c>
-      <c r="I15" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" t="s">
-        <v>41</v>
-      </c>
-      <c r="L15" t="s">
-        <v>41</v>
-      </c>
-      <c r="M15" t="s">
-        <v>41</v>
-      </c>
-      <c r="N15" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P15" s="60" t="s">
-        <v>41</v>
+      <c r="I15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O15" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="72" t="s">
+        <v>50</v>
       </c>
       <c r="Q15" t="s">
         <v>41</v>
@@ -3995,12 +4209,12 @@
       <c r="AH15" s="79"/>
       <c r="AI15" s="79"/>
       <c r="AJ15" s="79"/>
-      <c r="AK15" s="80" t="s">
-        <v>57</v>
+      <c r="AK15" s="63" t="s">
+        <v>44</v>
       </c>
       <c r="AL15" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-17</v>
       </c>
       <c r="AM15" s="64">
         <f t="shared" si="9"/>
@@ -4064,94 +4278,96 @@
       <c r="B16" s="55">
         <v>1600</v>
       </c>
-      <c r="C16" s="56"/>
+      <c r="C16" s="56">
+        <v>-272</v>
+      </c>
       <c r="D16" s="55">
         <f>(SUM(粮草!A16:X16)+AG16*10*IF(AK16="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2316</v>
       </c>
       <c r="E16" s="57">
         <f>SUM($B$4:B16)+SUM($C$4:C16)-SUM($D$4:D16)</f>
-        <v>26000</v>
+        <v>1242</v>
       </c>
       <c r="F16" s="55">
         <f>SUM(经验!A16:X16)</f>
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="G16" s="55">
         <f>SUM($F$4:F16)+SUM($H$4:H16)</f>
-        <v>1500</v>
+        <v>9030</v>
       </c>
       <c r="H16" s="55">
         <v>200</v>
       </c>
-      <c r="I16" t="s">
-        <v>41</v>
-      </c>
-      <c r="J16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" t="s">
-        <v>41</v>
-      </c>
-      <c r="L16" t="s">
-        <v>41</v>
-      </c>
-      <c r="M16" t="s">
-        <v>41</v>
-      </c>
-      <c r="N16" t="s">
-        <v>41</v>
-      </c>
-      <c r="O16" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P16" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>41</v>
-      </c>
-      <c r="R16" t="s">
-        <v>41</v>
-      </c>
-      <c r="S16" t="s">
-        <v>41</v>
-      </c>
-      <c r="T16" t="s">
-        <v>41</v>
-      </c>
-      <c r="U16" t="s">
-        <v>41</v>
-      </c>
-      <c r="V16" t="s">
-        <v>41</v>
-      </c>
-      <c r="W16" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="X16" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE16" s="60" t="s">
-        <v>41</v>
+      <c r="I16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="R16" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="S16" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="T16" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="U16" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="V16" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="W16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="X16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC16" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD16" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE16" s="71" t="s">
+        <v>49</v>
       </c>
       <c r="AF16" s="60" t="s">
         <v>41</v>
@@ -4168,15 +4384,15 @@
       </c>
       <c r="AL16" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-19</v>
       </c>
       <c r="AM16" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AN16" s="64">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AO16" s="83" t="s">
         <v>61</v>
@@ -4237,116 +4453,122 @@
       <c r="C17" s="56"/>
       <c r="D17" s="55">
         <f>(SUM(粮草!A17:X17)+AG17*10*IF(AK17="是",$BB$4,$BB$3))</f>
-        <v>0</v>
+        <v>2512</v>
       </c>
       <c r="E17" s="57">
         <f>SUM($B$4:B17)+SUM($C$4:C17)-SUM($D$4:D17)</f>
-        <v>27600</v>
+        <v>330</v>
       </c>
       <c r="F17" s="55">
         <f>SUM(经验!A17:X17)</f>
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="G17" s="55">
         <f>SUM($F$4:F17)+SUM($H$4:H17)</f>
-        <v>1500</v>
+        <v>10005</v>
       </c>
       <c r="H17" s="55">
         <v>0</v>
       </c>
-      <c r="I17" t="s">
-        <v>41</v>
-      </c>
-      <c r="J17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" t="s">
-        <v>41</v>
-      </c>
-      <c r="L17" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" t="s">
-        <v>41</v>
-      </c>
-      <c r="O17" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="P17" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>41</v>
-      </c>
-      <c r="R17" t="s">
-        <v>41</v>
-      </c>
-      <c r="S17" t="s">
-        <v>41</v>
-      </c>
-      <c r="T17" t="s">
-        <v>41</v>
-      </c>
-      <c r="U17" t="s">
-        <v>41</v>
-      </c>
-      <c r="V17" t="s">
-        <v>41</v>
-      </c>
-      <c r="W17" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="X17" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE17" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF17" s="60" t="s">
-        <v>41</v>
+      <c r="I17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="K17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="O17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="P17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="T17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="U17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="V17" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="W17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="X17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE17" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF17" s="71" t="s">
+        <v>49</v>
       </c>
       <c r="AG17" s="62">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH17" s="79"/>
-      <c r="AI17" s="79"/>
-      <c r="AJ17" s="79"/>
+        <v>17</v>
+      </c>
+      <c r="AH17" s="79">
+        <v>13</v>
+      </c>
+      <c r="AI17" s="79">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="79">
+        <v>3</v>
+      </c>
       <c r="AK17" s="80" t="s">
         <v>57</v>
       </c>
       <c r="AL17" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-21</v>
       </c>
       <c r="AM17" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AN17" s="64">
         <f t="shared" si="10"/>
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AO17" s="59" t="s">
         <v>40</v>
@@ -4366,15 +4588,15 @@
       </c>
       <c r="AT17" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU17" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV17" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW17">
         <v>18</v>
@@ -4385,15 +4607,15 @@
       </c>
       <c r="AY17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AZ17">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD17" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BE17" s="18"/>
     </row>
@@ -4411,7 +4633,7 @@
       </c>
       <c r="E18" s="57">
         <f>SUM($B$4:B18)+SUM($C$4:C18)-SUM($D$4:D18)</f>
-        <v>29200</v>
+        <v>1930</v>
       </c>
       <c r="F18" s="55">
         <f>SUM(经验!A18:X18)</f>
@@ -4419,7 +4641,7 @@
       </c>
       <c r="G18" s="55">
         <f>SUM($F$4:F18)+SUM($H$4:H18)</f>
-        <v>1500</v>
+        <v>10005</v>
       </c>
       <c r="H18" s="55">
         <v>0</v>
@@ -4508,11 +4730,11 @@
       </c>
       <c r="AL18" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-15</v>
       </c>
       <c r="AM18" s="64">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN18" s="64">
         <f t="shared" si="10"/>
@@ -4536,15 +4758,15 @@
       </c>
       <c r="AT18" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU18" s="65">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV18" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW18">
         <v>15</v>
@@ -4563,7 +4785,7 @@
       </c>
       <c r="BD18" s="67">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE18" s="18"/>
     </row>
@@ -4581,7 +4803,7 @@
       </c>
       <c r="E19" s="57">
         <f>SUM($B$4:B19)+SUM($C$4:C19)-SUM($D$4:D19)</f>
-        <v>30800</v>
+        <v>3530</v>
       </c>
       <c r="F19" s="55">
         <f>SUM(经验!A19:X19)</f>
@@ -4589,7 +4811,7 @@
       </c>
       <c r="G19" s="55">
         <f>SUM($F$4:F19)+SUM($H$4:H19)</f>
-        <v>1500</v>
+        <v>10005</v>
       </c>
       <c r="H19" s="55">
         <v>0</v>
@@ -4678,7 +4900,7 @@
       </c>
       <c r="AL19" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="AM19" s="64">
         <f t="shared" si="9"/>
@@ -4704,7 +4926,7 @@
       </c>
       <c r="AT19" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU19" s="65">
         <f t="shared" si="5"/>
@@ -4712,7 +4934,7 @@
       </c>
       <c r="AV19" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW19">
         <v>3</v>
@@ -4723,7 +4945,7 @@
       </c>
       <c r="AY19">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="AZ19">
         <f t="shared" si="2"/>
@@ -4749,7 +4971,7 @@
       </c>
       <c r="E20" s="57">
         <f>SUM($B$4:B20)+SUM($C$4:C20)-SUM($D$4:D20)</f>
-        <v>32400</v>
+        <v>5130</v>
       </c>
       <c r="F20" s="55">
         <f>SUM(经验!A20:X20)</f>
@@ -4757,7 +4979,7 @@
       </c>
       <c r="G20" s="55">
         <f>SUM($F$4:F20)+SUM($H$4:H20)</f>
-        <v>1500</v>
+        <v>10005</v>
       </c>
       <c r="H20" s="55">
         <v>0</v>
@@ -4846,7 +5068,7 @@
       </c>
       <c r="AL20" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="AM20" s="64">
         <f t="shared" si="9"/>
@@ -4872,7 +5094,7 @@
       </c>
       <c r="AT20" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU20" s="65">
         <f t="shared" si="5"/>
@@ -4880,7 +5102,7 @@
       </c>
       <c r="AV20" s="74">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW20">
         <v>5</v>
@@ -4891,7 +5113,7 @@
       </c>
       <c r="AY20">
         <f t="shared" ref="AY20:AY29" si="11">AT20*$AQ20</f>
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AZ20">
         <f t="shared" ref="AZ20:AZ29" si="12">AU20*$AQ20</f>
@@ -4917,7 +5139,7 @@
       </c>
       <c r="E21" s="57">
         <f>SUM($B$4:B21)+SUM($C$4:C21)-SUM($D$4:D21)</f>
-        <v>34000</v>
+        <v>6730</v>
       </c>
       <c r="F21" s="55">
         <f>SUM(经验!A21:X21)</f>
@@ -4925,7 +5147,7 @@
       </c>
       <c r="G21" s="55">
         <f>SUM($F$4:F21)+SUM($H$4:H21)</f>
-        <v>1700</v>
+        <v>10205</v>
       </c>
       <c r="H21" s="67">
         <v>200</v>
@@ -5014,7 +5236,7 @@
       </c>
       <c r="AL21" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AM21" s="64">
         <f t="shared" si="9"/>
@@ -5085,7 +5307,7 @@
       </c>
       <c r="E22" s="57">
         <f>SUM($B$4:B22)+SUM($C$4:C22)-SUM($D$4:D22)</f>
-        <v>35600</v>
+        <v>8330</v>
       </c>
       <c r="F22" s="55">
         <f>SUM(经验!A22:X22)</f>
@@ -5093,7 +5315,7 @@
       </c>
       <c r="G22" s="55">
         <f>SUM($F$4:F22)+SUM($H$4:H22)</f>
-        <v>1800</v>
+        <v>10305</v>
       </c>
       <c r="H22" s="67">
         <v>100</v>
@@ -5182,7 +5404,7 @@
       </c>
       <c r="AL22" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="AM22" s="64">
         <f t="shared" si="9"/>
@@ -5255,7 +5477,7 @@
       </c>
       <c r="E23" s="57">
         <f>SUM($B$4:B23)+SUM($C$4:C23)-SUM($D$4:D23)</f>
-        <v>37200</v>
+        <v>9930</v>
       </c>
       <c r="F23" s="55">
         <f>SUM(经验!A23:X23)</f>
@@ -5263,7 +5485,7 @@
       </c>
       <c r="G23" s="55">
         <f>SUM($F$4:F23)+SUM($H$4:H23)</f>
-        <v>2000</v>
+        <v>10505</v>
       </c>
       <c r="H23" s="67">
         <v>200</v>
@@ -5352,7 +5574,7 @@
       </c>
       <c r="AL23" s="64">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AM23" s="64">
         <f t="shared" si="9"/>
@@ -5423,7 +5645,7 @@
       </c>
       <c r="E24" s="57">
         <f>SUM($B$4:B24)+SUM($C$4:C24)-SUM($D$4:D24)</f>
-        <v>38800</v>
+        <v>11530</v>
       </c>
       <c r="F24" s="55">
         <f>SUM(经验!A24:X24)</f>
@@ -5431,7 +5653,7 @@
       </c>
       <c r="G24" s="55">
         <f>SUM($F$4:F24)+SUM($H$4:H24)</f>
-        <v>2000</v>
+        <v>10505</v>
       </c>
       <c r="H24" s="67">
         <v>0</v>
@@ -5593,7 +5815,7 @@
       </c>
       <c r="E25" s="57">
         <f>SUM($B$4:B25)+SUM($C$4:C25)-SUM($D$4:D25)</f>
-        <v>40400</v>
+        <v>13130</v>
       </c>
       <c r="F25" s="55">
         <f>SUM(经验!A25:X25)</f>
@@ -5601,7 +5823,7 @@
       </c>
       <c r="G25" s="55">
         <f>SUM($F$4:F25)+SUM($H$4:H25)</f>
-        <v>2000</v>
+        <v>10505</v>
       </c>
       <c r="H25" s="67">
         <v>0</v>
@@ -5763,7 +5985,7 @@
       </c>
       <c r="E26" s="57">
         <f>SUM($B$4:B26)+SUM($C$4:C26)-SUM($D$4:D26)</f>
-        <v>42000</v>
+        <v>14730</v>
       </c>
       <c r="F26" s="55">
         <f>SUM(经验!A26:X26)</f>
@@ -5771,7 +5993,7 @@
       </c>
       <c r="G26" s="55">
         <f>SUM($F$4:F26)+SUM($H$4:H26)</f>
-        <v>2000</v>
+        <v>10505</v>
       </c>
       <c r="H26" s="67">
         <v>0</v>
@@ -5933,7 +6155,7 @@
       </c>
       <c r="E27" s="57">
         <f>SUM($B$4:B27)+SUM($C$4:C27)-SUM($D$4:D27)</f>
-        <v>43600</v>
+        <v>16330</v>
       </c>
       <c r="F27" s="55">
         <f>SUM(经验!A27:X27)</f>
@@ -5941,7 +6163,7 @@
       </c>
       <c r="G27" s="55">
         <f>SUM($F$4:F27)+SUM($H$4:H27)</f>
-        <v>2000</v>
+        <v>10505</v>
       </c>
       <c r="H27" s="67">
         <v>0</v>
@@ -6103,7 +6325,7 @@
       </c>
       <c r="E28" s="57">
         <f>SUM($B$4:B28)+SUM($C$4:C28)-SUM($D$4:D28)</f>
-        <v>45200</v>
+        <v>17930</v>
       </c>
       <c r="F28" s="55">
         <f>SUM(经验!A28:X28)</f>
@@ -6111,7 +6333,7 @@
       </c>
       <c r="G28" s="55">
         <f>SUM($F$4:F28)+SUM($H$4:H28)</f>
-        <v>2200</v>
+        <v>10705</v>
       </c>
       <c r="H28" s="55">
         <v>200</v>
@@ -6268,7 +6490,7 @@
       </c>
       <c r="E29" s="57">
         <f>SUM($B$4:B29)+SUM($C$4:C29)-SUM($D$4:D29)</f>
-        <v>46800</v>
+        <v>19530</v>
       </c>
       <c r="F29" s="55">
         <f>SUM(经验!A29:X29)</f>
@@ -6276,7 +6498,7 @@
       </c>
       <c r="G29" s="55">
         <f>SUM($F$4:F29)+SUM($H$4:H29)</f>
-        <v>2300</v>
+        <v>10805</v>
       </c>
       <c r="H29" s="55">
         <v>100</v>
@@ -6436,7 +6658,7 @@
       </c>
       <c r="E30" s="57">
         <f>SUM($B$4:B30)+SUM($C$4:C30)-SUM($D$4:D30)</f>
-        <v>48400</v>
+        <v>21130</v>
       </c>
       <c r="F30" s="55">
         <f>SUM(经验!A30:X30)</f>
@@ -6444,7 +6666,7 @@
       </c>
       <c r="G30" s="55">
         <f>SUM($F$4:F30)+SUM($H$4:H30)</f>
-        <v>2500</v>
+        <v>11005</v>
       </c>
       <c r="H30" s="55">
         <v>200</v>
@@ -6548,7 +6770,7 @@
       <c r="AQ30" s="14"/>
       <c r="BD30" s="67">
         <f>SUM(BD4:BD29)+AG2*10</f>
-        <v>0</v>
+        <v>6539.9952127948918</v>
       </c>
       <c r="BE30" s="18"/>
     </row>
@@ -6566,7 +6788,7 @@
       </c>
       <c r="E31" s="57">
         <f>SUM($B$4:B31)+SUM($C$4:C31)-SUM($D$4:D31)</f>
-        <v>50000</v>
+        <v>22730</v>
       </c>
       <c r="F31" s="55">
         <f>SUM(经验!A31:X31)</f>
@@ -6574,7 +6796,7 @@
       </c>
       <c r="G31" s="55">
         <f>SUM($F$4:F31)+SUM($H$4:H31)</f>
-        <v>2500</v>
+        <v>11005</v>
       </c>
       <c r="H31" s="55">
         <v>0</v>
@@ -6692,7 +6914,7 @@
       </c>
       <c r="E32" s="57">
         <f>SUM($B$4:B32)+SUM($C$4:C32)-SUM($D$4:D32)</f>
-        <v>51600</v>
+        <v>24330</v>
       </c>
       <c r="F32" s="55">
         <f>SUM(经验!A32:X32)</f>
@@ -6700,7 +6922,7 @@
       </c>
       <c r="G32" s="55">
         <f>SUM($F$4:F32)+SUM($H$4:H32)</f>
-        <v>2500</v>
+        <v>11005</v>
       </c>
       <c r="H32" s="55">
         <v>0</v>
@@ -6836,7 +7058,7 @@
       </c>
       <c r="E33" s="57">
         <f>SUM($B$4:B33)+SUM($C$4:C33)-SUM($D$4:D33)</f>
-        <v>53200</v>
+        <v>25930</v>
       </c>
       <c r="F33" s="55">
         <f>SUM(经验!A33:X33)</f>
@@ -6844,7 +7066,7 @@
       </c>
       <c r="G33" s="55">
         <f>SUM($F$4:F33)+SUM($H$4:H33)</f>
-        <v>2500</v>
+        <v>11005</v>
       </c>
       <c r="H33" s="55">
         <v>0</v>
@@ -6951,15 +7173,15 @@
       </c>
       <c r="AQ33" s="14">
         <f t="shared" ref="AQ33:AQ36" si="15">AP33-AV6</f>
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="AR33">
         <f t="shared" ref="AR33:AR36" si="16">AQ33*AP6*0.8</f>
-        <v>26248</v>
+        <v>11696</v>
       </c>
       <c r="AS33">
         <f t="shared" ref="AS33:AS38" si="17">AQ33*AQ6</f>
-        <v>8685</v>
+        <v>3870</v>
       </c>
       <c r="AU33" s="101" t="s">
         <v>99</v>
@@ -6983,7 +7205,7 @@
       </c>
       <c r="E34" s="57">
         <f>SUM($B$4:B34)+SUM($C$4:C34)-SUM($D$4:D34)</f>
-        <v>54800</v>
+        <v>27530</v>
       </c>
       <c r="F34" s="55">
         <f>SUM(经验!A34:X34)</f>
@@ -6991,7 +7213,7 @@
       </c>
       <c r="G34" s="55">
         <f>SUM($F$4:F34)+SUM($H$4:H34)</f>
-        <v>2500</v>
+        <v>11005</v>
       </c>
       <c r="H34" s="55">
         <v>0</v>
@@ -7098,15 +7320,15 @@
       </c>
       <c r="AQ34" s="14">
         <f t="shared" si="15"/>
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="AR34">
         <f t="shared" si="16"/>
-        <v>38304</v>
+        <v>36144</v>
       </c>
       <c r="AS34">
         <f t="shared" si="17"/>
-        <v>13300</v>
+        <v>12550</v>
       </c>
       <c r="BE34" s="18"/>
     </row>
@@ -7124,7 +7346,7 @@
       </c>
       <c r="E35" s="57">
         <f>SUM($B$4:B35)+SUM($C$4:C35)-SUM($D$4:D35)</f>
-        <v>56400</v>
+        <v>29130</v>
       </c>
       <c r="F35" s="55">
         <f>SUM(经验!A35:X35)</f>
@@ -7132,7 +7354,7 @@
       </c>
       <c r="G35" s="55">
         <f>SUM($F$4:F35)+SUM($H$4:H35)</f>
-        <v>2700</v>
+        <v>11205</v>
       </c>
       <c r="H35" s="67">
         <v>200</v>
@@ -7265,7 +7487,7 @@
       </c>
       <c r="E36" s="57">
         <f>SUM($B$4:B36)+SUM($C$4:C36)-SUM($D$4:D36)</f>
-        <v>58000</v>
+        <v>30730</v>
       </c>
       <c r="F36" s="55">
         <f>SUM(经验!A36:X36)</f>
@@ -7273,7 +7495,7 @@
       </c>
       <c r="G36" s="55">
         <f>SUM($F$4:F36)+SUM($H$4:H36)</f>
-        <v>2800</v>
+        <v>11305</v>
       </c>
       <c r="H36" s="67">
         <v>100</v>
@@ -7406,7 +7628,7 @@
       </c>
       <c r="E37" s="57">
         <f>SUM($B$4:B37)+SUM($C$4:C37)-SUM($D$4:D37)</f>
-        <v>59600</v>
+        <v>32330</v>
       </c>
       <c r="F37" s="55">
         <f>SUM(经验!A37:X37)</f>
@@ -7414,7 +7636,7 @@
       </c>
       <c r="G37" s="55">
         <f>SUM($F$4:F37)+SUM($H$4:H37)</f>
-        <v>3000</v>
+        <v>11505</v>
       </c>
       <c r="H37" s="67">
         <v>200</v>
@@ -7521,15 +7743,15 @@
       </c>
       <c r="AQ37" s="14">
         <f>AP37-AV17</f>
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AR37">
         <f>AQ37*AP17*0.8</f>
-        <v>1520</v>
+        <v>1080</v>
       </c>
       <c r="AS37">
         <f>AQ37*AQ17</f>
-        <v>1140</v>
+        <v>810</v>
       </c>
       <c r="BE37" s="18"/>
     </row>
@@ -7547,7 +7769,7 @@
       </c>
       <c r="E38" s="57">
         <f>SUM($B$4:B38)+SUM($C$4:C38)-SUM($D$4:D38)</f>
-        <v>61200</v>
+        <v>33930</v>
       </c>
       <c r="F38" s="55">
         <f>SUM(经验!A38:X38)</f>
@@ -7555,7 +7777,7 @@
       </c>
       <c r="G38" s="55">
         <f>SUM($F$4:F38)+SUM($H$4:H38)</f>
-        <v>3000</v>
+        <v>11505</v>
       </c>
       <c r="H38" s="67">
         <v>0</v>
@@ -7662,15 +7884,15 @@
       </c>
       <c r="AQ38" s="14">
         <f>AP38-AV11-AV26</f>
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="AR38">
         <f t="shared" ref="AR38:AR42" si="19">AQ38*AP11*0.8</f>
-        <v>5040</v>
+        <v>3960</v>
       </c>
       <c r="AS38">
         <f t="shared" si="17"/>
-        <v>1680</v>
+        <v>1320</v>
       </c>
       <c r="BE38" s="18"/>
     </row>
@@ -7688,7 +7910,7 @@
       </c>
       <c r="E39" s="57">
         <f>SUM($B$4:B39)+SUM($C$4:C39)-SUM($D$4:D39)</f>
-        <v>62800</v>
+        <v>35530</v>
       </c>
       <c r="F39" s="55">
         <f>SUM(经验!A39:X39)</f>
@@ -7696,7 +7918,7 @@
       </c>
       <c r="G39" s="55">
         <f>SUM($F$4:F39)+SUM($H$4:H39)</f>
-        <v>3000</v>
+        <v>11505</v>
       </c>
       <c r="H39" s="67">
         <v>0</v>
@@ -7803,15 +8025,15 @@
       </c>
       <c r="AQ39" s="14">
         <f>AP39-AV12-AV27</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR39">
         <f t="shared" si="19"/>
-        <v>720</v>
+        <v>600</v>
       </c>
       <c r="AS39">
         <f t="shared" si="18"/>
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="BE39" s="18"/>
     </row>
@@ -7829,7 +8051,7 @@
       </c>
       <c r="E40" s="57">
         <f>SUM($B$4:B40)+SUM($C$4:C40)-SUM($D$4:D40)</f>
-        <v>64400</v>
+        <v>37130</v>
       </c>
       <c r="F40" s="55">
         <f>SUM(经验!A40:X40)</f>
@@ -7837,7 +8059,7 @@
       </c>
       <c r="G40" s="55">
         <f>SUM($F$4:F40)+SUM($H$4:H40)</f>
-        <v>3000</v>
+        <v>11505</v>
       </c>
       <c r="H40" s="67">
         <v>0</v>
@@ -7970,7 +8192,7 @@
       </c>
       <c r="E41" s="57">
         <f>SUM($B$4:B41)+SUM($C$4:C41)-SUM($D$4:D41)</f>
-        <v>66000</v>
+        <v>38730</v>
       </c>
       <c r="F41" s="55">
         <f>SUM(经验!A41:X41)</f>
@@ -7978,7 +8200,7 @@
       </c>
       <c r="G41" s="55">
         <f>SUM($F$4:F41)+SUM($H$4:H41)</f>
-        <v>3000</v>
+        <v>11505</v>
       </c>
       <c r="H41" s="67">
         <v>0</v>
@@ -8111,7 +8333,7 @@
       </c>
       <c r="E42" s="57">
         <f>SUM($B$4:B42)+SUM($C$4:C42)-SUM($D$4:D42)</f>
-        <v>67600</v>
+        <v>40330</v>
       </c>
       <c r="F42" s="55">
         <f>SUM(经验!A42:X42)</f>
@@ -8119,7 +8341,7 @@
       </c>
       <c r="G42" s="55">
         <f>SUM($F$4:F42)+SUM($H$4:H42)</f>
-        <v>3300</v>
+        <v>11805</v>
       </c>
       <c r="H42" s="55">
         <v>300</v>
@@ -8252,7 +8474,7 @@
       </c>
       <c r="E43" s="57">
         <f>SUM($B$4:B43)+SUM($C$4:C43)-SUM($D$4:D43)</f>
-        <v>69200</v>
+        <v>41930</v>
       </c>
       <c r="F43" s="55">
         <f>SUM(经验!A43:X43)</f>
@@ -8260,7 +8482,7 @@
       </c>
       <c r="G43" s="55">
         <f>SUM($F$4:F43)+SUM($H$4:H43)</f>
-        <v>3300</v>
+        <v>11805</v>
       </c>
       <c r="H43" s="55">
         <v>0</v>
@@ -8393,7 +8615,7 @@
       </c>
       <c r="E44" s="57">
         <f>SUM($B$4:B44)+SUM($C$4:C44)-SUM($D$4:D44)</f>
-        <v>70800</v>
+        <v>43530</v>
       </c>
       <c r="F44" s="55">
         <f>SUM(经验!A44:X44)</f>
@@ -8401,7 +8623,7 @@
       </c>
       <c r="G44" s="55">
         <f>SUM($F$4:F44)+SUM($H$4:H44)</f>
-        <v>3500</v>
+        <v>12005</v>
       </c>
       <c r="H44" s="55">
         <v>200</v>
@@ -8534,7 +8756,7 @@
       </c>
       <c r="E45" s="57">
         <f>SUM($B$4:B45)+SUM($C$4:C45)-SUM($D$4:D45)</f>
-        <v>72400</v>
+        <v>45130</v>
       </c>
       <c r="F45" s="55">
         <f>SUM(经验!A45:X45)</f>
@@ -8542,7 +8764,7 @@
       </c>
       <c r="G45" s="55">
         <f>SUM($F$4:F45)+SUM($H$4:H45)</f>
-        <v>3500</v>
+        <v>12005</v>
       </c>
       <c r="H45" s="55">
         <v>0</v>
@@ -8675,7 +8897,7 @@
       </c>
       <c r="E46" s="57">
         <f>SUM($B$4:B46)+SUM($C$4:C46)-SUM($D$4:D46)</f>
-        <v>74000</v>
+        <v>46730</v>
       </c>
       <c r="F46" s="55">
         <f>SUM(经验!A46:X46)</f>
@@ -8683,7 +8905,7 @@
       </c>
       <c r="G46" s="55">
         <f>SUM($F$4:F46)+SUM($H$4:H46)</f>
-        <v>3500</v>
+        <v>12005</v>
       </c>
       <c r="H46" s="55">
         <v>0</v>
@@ -8787,15 +9009,15 @@
       </c>
       <c r="AQ46">
         <f>SUM(AQ33:AQ43)</f>
-        <v>970</v>
+        <v>827</v>
       </c>
       <c r="AR46">
         <f>SUM(AR33:AR45)</f>
-        <v>138400</v>
+        <v>120048</v>
       </c>
       <c r="AS46">
         <f>SUM(AS33:AS45)</f>
-        <v>53875</v>
+        <v>47575</v>
       </c>
       <c r="BE46" s="18"/>
     </row>
@@ -8813,7 +9035,7 @@
       </c>
       <c r="E47" s="57">
         <f>SUM($B$4:B47)+SUM($C$4:C47)-SUM($D$4:D47)</f>
-        <v>75600</v>
+        <v>48330</v>
       </c>
       <c r="F47" s="55">
         <f>SUM(经验!A47:X47)</f>
@@ -8821,7 +9043,7 @@
       </c>
       <c r="G47" s="55">
         <f>SUM($F$4:F47)+SUM($H$4:H47)</f>
-        <v>3500</v>
+        <v>12005</v>
       </c>
       <c r="H47" s="55">
         <v>0</v>
@@ -8925,11 +9147,11 @@
       </c>
       <c r="AR47" s="88">
         <f>E93-AR46</f>
-        <v>10800</v>
+        <v>1882</v>
       </c>
       <c r="AS47" s="88">
         <f>AS46+G93+AV33</f>
-        <v>63161</v>
+        <v>65366</v>
       </c>
       <c r="BE47" s="18"/>
     </row>
@@ -8947,7 +9169,7 @@
       </c>
       <c r="E48" s="57">
         <f>SUM($B$4:B48)+SUM($C$4:C48)-SUM($D$4:D48)</f>
-        <v>77200</v>
+        <v>49930</v>
       </c>
       <c r="F48" s="55">
         <f>SUM(经验!A48:X48)</f>
@@ -8955,7 +9177,7 @@
       </c>
       <c r="G48" s="55">
         <f>SUM($F$4:F48)+SUM($H$4:H48)</f>
-        <v>3500</v>
+        <v>12005</v>
       </c>
       <c r="H48" s="55">
         <v>0</v>
@@ -9056,10 +9278,10 @@
       </c>
       <c r="AO48" s="14"/>
       <c r="AP48" s="14"/>
-      <c r="AQ48" s="102" t="s">
+      <c r="AQ48" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="AR48" s="102"/>
+      <c r="AR48" s="103"/>
       <c r="AS48" s="14"/>
       <c r="AT48" s="14"/>
       <c r="BE48" s="18"/>
@@ -9078,7 +9300,7 @@
       </c>
       <c r="E49" s="57">
         <f>SUM($B$4:B49)+SUM($C$4:C49)-SUM($D$4:D49)</f>
-        <v>78800</v>
+        <v>51530</v>
       </c>
       <c r="F49" s="55">
         <f>SUM(经验!A49:X49)</f>
@@ -9086,7 +9308,7 @@
       </c>
       <c r="G49" s="55">
         <f>SUM($F$4:F49)+SUM($H$4:H49)</f>
-        <v>3700</v>
+        <v>12205</v>
       </c>
       <c r="H49" s="67">
         <v>200</v>
@@ -9217,7 +9439,7 @@
       </c>
       <c r="E50" s="57">
         <f>SUM($B$4:B50)+SUM($C$4:C50)-SUM($D$4:D50)</f>
-        <v>80400</v>
+        <v>53130</v>
       </c>
       <c r="F50" s="55">
         <f>SUM(经验!A50:X50)</f>
@@ -9225,7 +9447,7 @@
       </c>
       <c r="G50" s="55">
         <f>SUM($F$4:F50)+SUM($H$4:H50)</f>
-        <v>3800</v>
+        <v>12305</v>
       </c>
       <c r="H50" s="67">
         <v>100</v>
@@ -9340,11 +9562,11 @@
       </c>
       <c r="AS50" s="99">
         <f>COUNTIF(I4:AF17,$AO$18)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT50" s="14">
         <f>AP50*AS50</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AV50">
         <v>9</v>
@@ -9382,7 +9604,7 @@
       </c>
       <c r="E51" s="57">
         <f>SUM($B$4:B51)+SUM($C$4:C51)-SUM($D$4:D51)</f>
-        <v>82000</v>
+        <v>54730</v>
       </c>
       <c r="F51" s="55">
         <f>SUM(经验!A51:X51)</f>
@@ -9390,7 +9612,7 @@
       </c>
       <c r="G51" s="55">
         <f>SUM($F$4:F51)+SUM($H$4:H51)</f>
-        <v>4000</v>
+        <v>12505</v>
       </c>
       <c r="H51" s="67">
         <v>200</v>
@@ -9533,7 +9755,7 @@
       </c>
       <c r="E52" s="57">
         <f>SUM($B$4:B52)+SUM($C$4:C52)-SUM($D$4:D52)</f>
-        <v>83600</v>
+        <v>56330</v>
       </c>
       <c r="F52" s="55">
         <f>SUM(经验!A52:X52)</f>
@@ -9541,7 +9763,7 @@
       </c>
       <c r="G52" s="55">
         <f>SUM($F$4:F52)+SUM($H$4:H52)</f>
-        <v>4000</v>
+        <v>12505</v>
       </c>
       <c r="H52" s="67">
         <v>0</v>
@@ -9678,7 +9900,7 @@
       </c>
       <c r="E53" s="57">
         <f>SUM($B$4:B53)+SUM($C$4:C53)-SUM($D$4:D53)</f>
-        <v>85200</v>
+        <v>57930</v>
       </c>
       <c r="F53" s="55">
         <f>SUM(经验!A53:X53)</f>
@@ -9686,7 +9908,7 @@
       </c>
       <c r="G53" s="55">
         <f>SUM($F$4:F53)+SUM($H$4:H53)</f>
-        <v>4000</v>
+        <v>12505</v>
       </c>
       <c r="H53" s="67">
         <v>0</v>
@@ -9823,7 +10045,7 @@
       </c>
       <c r="E54" s="57">
         <f>SUM($B$4:B54)+SUM($C$4:C54)-SUM($D$4:D54)</f>
-        <v>86800</v>
+        <v>59530</v>
       </c>
       <c r="F54" s="55">
         <f>SUM(经验!A54:X54)</f>
@@ -9831,7 +10053,7 @@
       </c>
       <c r="G54" s="55">
         <f>SUM($F$4:F54)+SUM($H$4:H54)</f>
-        <v>4000</v>
+        <v>12505</v>
       </c>
       <c r="H54" s="67">
         <v>0</v>
@@ -9968,7 +10190,7 @@
       </c>
       <c r="E55" s="57">
         <f>SUM($B$4:B55)+SUM($C$4:C55)-SUM($D$4:D55)</f>
-        <v>88400</v>
+        <v>61130</v>
       </c>
       <c r="F55" s="55">
         <f>SUM(经验!A55:X55)</f>
@@ -9976,7 +10198,7 @@
       </c>
       <c r="G55" s="55">
         <f>SUM($F$4:F55)+SUM($H$4:H55)</f>
-        <v>4000</v>
+        <v>12505</v>
       </c>
       <c r="H55" s="67">
         <v>0</v>
@@ -10082,7 +10304,7 @@
       <c r="AS55" s="14"/>
       <c r="AT55" s="14">
         <f>SUM(AT50:AT54)</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="BE55" s="18"/>
     </row>
@@ -10100,7 +10322,7 @@
       </c>
       <c r="E56" s="57">
         <f>SUM($B$4:B56)+SUM($C$4:C56)-SUM($D$4:D56)</f>
-        <v>90000</v>
+        <v>62730</v>
       </c>
       <c r="F56" s="55">
         <f>SUM(经验!A56:X56)</f>
@@ -10108,7 +10330,7 @@
       </c>
       <c r="G56" s="55">
         <f>SUM($F$4:F56)+SUM($H$4:H56)</f>
-        <v>4300</v>
+        <v>12805</v>
       </c>
       <c r="H56" s="55">
         <v>300</v>
@@ -10223,7 +10445,7 @@
       </c>
       <c r="E57" s="57">
         <f>SUM($B$4:B57)+SUM($C$4:C57)-SUM($D$4:D57)</f>
-        <v>91600</v>
+        <v>64330</v>
       </c>
       <c r="F57" s="55">
         <f>SUM(经验!A57:X57)</f>
@@ -10231,7 +10453,7 @@
       </c>
       <c r="G57" s="55">
         <f>SUM($F$4:F57)+SUM($H$4:H57)</f>
-        <v>4300</v>
+        <v>12805</v>
       </c>
       <c r="H57" s="55">
         <v>0</v>
@@ -10346,7 +10568,7 @@
       </c>
       <c r="E58" s="57">
         <f>SUM($B$4:B58)+SUM($C$4:C58)-SUM($D$4:D58)</f>
-        <v>93200</v>
+        <v>65930</v>
       </c>
       <c r="F58" s="55">
         <f>SUM(经验!A58:X58)</f>
@@ -10354,7 +10576,7 @@
       </c>
       <c r="G58" s="55">
         <f>SUM($F$4:F58)+SUM($H$4:H58)</f>
-        <v>4500</v>
+        <v>13005</v>
       </c>
       <c r="H58" s="55">
         <v>200</v>
@@ -10469,7 +10691,7 @@
       </c>
       <c r="E59" s="57">
         <f>SUM($B$4:B59)+SUM($C$4:C59)-SUM($D$4:D59)</f>
-        <v>94800</v>
+        <v>67530</v>
       </c>
       <c r="F59" s="55">
         <f>SUM(经验!A59:X59)</f>
@@ -10477,7 +10699,7 @@
       </c>
       <c r="G59" s="55">
         <f>SUM($F$4:F59)+SUM($H$4:H59)</f>
-        <v>4500</v>
+        <v>13005</v>
       </c>
       <c r="H59" s="55">
         <v>0</v>
@@ -10592,7 +10814,7 @@
       </c>
       <c r="E60" s="57">
         <f>SUM($B$4:B60)+SUM($C$4:C60)-SUM($D$4:D60)</f>
-        <v>96400</v>
+        <v>69130</v>
       </c>
       <c r="F60" s="55">
         <f>SUM(经验!A60:X60)</f>
@@ -10600,7 +10822,7 @@
       </c>
       <c r="G60" s="55">
         <f>SUM($F$4:F60)+SUM($H$4:H60)</f>
-        <v>4500</v>
+        <v>13005</v>
       </c>
       <c r="H60" s="55">
         <v>0</v>
@@ -10715,7 +10937,7 @@
       </c>
       <c r="E61" s="57">
         <f>SUM($B$4:B61)+SUM($C$4:C61)-SUM($D$4:D61)</f>
-        <v>98000</v>
+        <v>70730</v>
       </c>
       <c r="F61" s="55">
         <f>SUM(经验!A61:X61)</f>
@@ -10723,7 +10945,7 @@
       </c>
       <c r="G61" s="55">
         <f>SUM($F$4:F61)+SUM($H$4:H61)</f>
-        <v>4500</v>
+        <v>13005</v>
       </c>
       <c r="H61" s="55">
         <v>0</v>
@@ -10838,7 +11060,7 @@
       </c>
       <c r="E62" s="57">
         <f>SUM($B$4:B62)+SUM($C$4:C62)-SUM($D$4:D62)</f>
-        <v>99600</v>
+        <v>72330</v>
       </c>
       <c r="F62" s="55">
         <f>SUM(经验!A62:X62)</f>
@@ -10846,7 +11068,7 @@
       </c>
       <c r="G62" s="55">
         <f>SUM($F$4:F62)+SUM($H$4:H62)</f>
-        <v>4500</v>
+        <v>13005</v>
       </c>
       <c r="H62" s="55">
         <v>0</v>
@@ -10961,7 +11183,7 @@
       </c>
       <c r="E63" s="57">
         <f>SUM($B$4:B63)+SUM($C$4:C63)-SUM($D$4:D63)</f>
-        <v>101200</v>
+        <v>73930</v>
       </c>
       <c r="F63" s="55">
         <f>SUM(经验!A63:X63)</f>
@@ -10969,7 +11191,7 @@
       </c>
       <c r="G63" s="55">
         <f>SUM($F$4:F63)+SUM($H$4:H63)</f>
-        <v>4800</v>
+        <v>13305</v>
       </c>
       <c r="H63" s="67">
         <v>300</v>
@@ -11084,7 +11306,7 @@
       </c>
       <c r="E64" s="57">
         <f>SUM($B$4:B64)+SUM($C$4:C64)-SUM($D$4:D64)</f>
-        <v>102800</v>
+        <v>75530</v>
       </c>
       <c r="F64" s="55">
         <f>SUM(经验!A64:X64)</f>
@@ -11092,7 +11314,7 @@
       </c>
       <c r="G64" s="55">
         <f>SUM($F$4:F64)+SUM($H$4:H64)</f>
-        <v>4800</v>
+        <v>13305</v>
       </c>
       <c r="H64" s="67">
         <v>0</v>
@@ -11207,7 +11429,7 @@
       </c>
       <c r="E65" s="57">
         <f>SUM($B$4:B65)+SUM($C$4:C65)-SUM($D$4:D65)</f>
-        <v>104400</v>
+        <v>77130</v>
       </c>
       <c r="F65" s="55">
         <f>SUM(经验!A65:X65)</f>
@@ -11215,7 +11437,7 @@
       </c>
       <c r="G65" s="55">
         <f>SUM($F$4:F65)+SUM($H$4:H65)</f>
-        <v>5000</v>
+        <v>13505</v>
       </c>
       <c r="H65" s="67">
         <v>200</v>
@@ -11330,7 +11552,7 @@
       </c>
       <c r="E66" s="57">
         <f>SUM($B$4:B66)+SUM($C$4:C66)-SUM($D$4:D66)</f>
-        <v>106000</v>
+        <v>78730</v>
       </c>
       <c r="F66" s="55">
         <f>SUM(经验!A66:X66)</f>
@@ -11338,7 +11560,7 @@
       </c>
       <c r="G66" s="55">
         <f>SUM($F$4:F66)+SUM($H$4:H66)</f>
-        <v>5000</v>
+        <v>13505</v>
       </c>
       <c r="H66" s="67">
         <v>0</v>
@@ -11453,7 +11675,7 @@
       </c>
       <c r="E67" s="57">
         <f>SUM($B$4:B67)+SUM($C$4:C67)-SUM($D$4:D67)</f>
-        <v>107600</v>
+        <v>80330</v>
       </c>
       <c r="F67" s="55">
         <f>SUM(经验!A67:X67)</f>
@@ -11461,7 +11683,7 @@
       </c>
       <c r="G67" s="55">
         <f>SUM($F$4:F67)+SUM($H$4:H67)</f>
-        <v>5000</v>
+        <v>13505</v>
       </c>
       <c r="H67" s="67">
         <v>0</v>
@@ -11576,7 +11798,7 @@
       </c>
       <c r="E68" s="57">
         <f>SUM($B$4:B68)+SUM($C$4:C68)-SUM($D$4:D68)</f>
-        <v>109200</v>
+        <v>81930</v>
       </c>
       <c r="F68" s="55">
         <f>SUM(经验!A68:X68)</f>
@@ -11584,7 +11806,7 @@
       </c>
       <c r="G68" s="55">
         <f>SUM($F$4:F68)+SUM($H$4:H68)</f>
-        <v>5000</v>
+        <v>13505</v>
       </c>
       <c r="H68" s="67">
         <v>0</v>
@@ -11699,7 +11921,7 @@
       </c>
       <c r="E69" s="57">
         <f>SUM($B$4:B69)+SUM($C$4:C69)-SUM($D$4:D69)</f>
-        <v>110800</v>
+        <v>83530</v>
       </c>
       <c r="F69" s="55">
         <f>SUM(经验!A69:X69)</f>
@@ -11707,7 +11929,7 @@
       </c>
       <c r="G69" s="55">
         <f>SUM($F$4:F69)+SUM($H$4:H69)</f>
-        <v>5000</v>
+        <v>13505</v>
       </c>
       <c r="H69" s="67">
         <v>0</v>
@@ -11822,7 +12044,7 @@
       </c>
       <c r="E70" s="57">
         <f>SUM($B$4:B70)+SUM($C$4:C70)-SUM($D$4:D70)</f>
-        <v>112400</v>
+        <v>85130</v>
       </c>
       <c r="F70" s="55">
         <f>SUM(经验!A70:X70)</f>
@@ -11830,7 +12052,7 @@
       </c>
       <c r="G70" s="55">
         <f>SUM($F$4:F70)+SUM($H$4:H70)</f>
-        <v>5300</v>
+        <v>13805</v>
       </c>
       <c r="H70" s="55">
         <v>300</v>
@@ -11945,7 +12167,7 @@
       </c>
       <c r="E71" s="57">
         <f>SUM($B$4:B71)+SUM($C$4:C71)-SUM($D$4:D71)</f>
-        <v>114000</v>
+        <v>86730</v>
       </c>
       <c r="F71" s="55">
         <f>SUM(经验!A71:X71)</f>
@@ -11953,7 +12175,7 @@
       </c>
       <c r="G71" s="55">
         <f>SUM($F$4:F71)+SUM($H$4:H71)</f>
-        <v>5300</v>
+        <v>13805</v>
       </c>
       <c r="H71" s="55">
         <v>0</v>
@@ -12068,7 +12290,7 @@
       </c>
       <c r="E72" s="57">
         <f>SUM($B$4:B72)+SUM($C$4:C72)-SUM($D$4:D72)</f>
-        <v>115600</v>
+        <v>88330</v>
       </c>
       <c r="F72" s="55">
         <f>SUM(经验!A72:X72)</f>
@@ -12076,7 +12298,7 @@
       </c>
       <c r="G72" s="55">
         <f>SUM($F$4:F72)+SUM($H$4:H72)</f>
-        <v>5500</v>
+        <v>14005</v>
       </c>
       <c r="H72" s="55">
         <v>200</v>
@@ -12191,7 +12413,7 @@
       </c>
       <c r="E73" s="57">
         <f>SUM($B$4:B73)+SUM($C$4:C73)-SUM($D$4:D73)</f>
-        <v>117200</v>
+        <v>89930</v>
       </c>
       <c r="F73" s="55">
         <f>SUM(经验!A73:X73)</f>
@@ -12199,7 +12421,7 @@
       </c>
       <c r="G73" s="55">
         <f>SUM($F$4:F73)+SUM($H$4:H73)</f>
-        <v>5500</v>
+        <v>14005</v>
       </c>
       <c r="H73" s="55">
         <v>0</v>
@@ -12314,7 +12536,7 @@
       </c>
       <c r="E74" s="57">
         <f>SUM($B$4:B74)+SUM($C$4:C74)-SUM($D$4:D74)</f>
-        <v>118800</v>
+        <v>91530</v>
       </c>
       <c r="F74" s="55">
         <f>SUM(经验!A74:X74)</f>
@@ -12322,7 +12544,7 @@
       </c>
       <c r="G74" s="55">
         <f>SUM($F$4:F74)+SUM($H$4:H74)</f>
-        <v>5500</v>
+        <v>14005</v>
       </c>
       <c r="H74" s="55">
         <v>0</v>
@@ -12437,7 +12659,7 @@
       </c>
       <c r="E75" s="57">
         <f>SUM($B$4:B75)+SUM($C$4:C75)-SUM($D$4:D75)</f>
-        <v>120400</v>
+        <v>93130</v>
       </c>
       <c r="F75" s="55">
         <f>SUM(经验!A75:X75)</f>
@@ -12445,7 +12667,7 @@
       </c>
       <c r="G75" s="55">
         <f>SUM($F$4:F75)+SUM($H$4:H75)</f>
-        <v>5500</v>
+        <v>14005</v>
       </c>
       <c r="H75" s="55">
         <v>0</v>
@@ -12560,7 +12782,7 @@
       </c>
       <c r="E76" s="57">
         <f>SUM($B$4:B76)+SUM($C$4:C76)-SUM($D$4:D76)</f>
-        <v>122000</v>
+        <v>94730</v>
       </c>
       <c r="F76" s="55">
         <f>SUM(经验!A76:X76)</f>
@@ -12568,7 +12790,7 @@
       </c>
       <c r="G76" s="55">
         <f>SUM($F$4:F76)+SUM($H$4:H76)</f>
-        <v>5500</v>
+        <v>14005</v>
       </c>
       <c r="H76" s="55">
         <v>0</v>
@@ -12683,7 +12905,7 @@
       </c>
       <c r="E77" s="57">
         <f>SUM($B$4:B77)+SUM($C$4:C77)-SUM($D$4:D77)</f>
-        <v>123600</v>
+        <v>96330</v>
       </c>
       <c r="F77" s="55">
         <f>SUM(经验!A77:X77)</f>
@@ -12691,7 +12913,7 @@
       </c>
       <c r="G77" s="55">
         <f>SUM($F$4:F77)+SUM($H$4:H77)</f>
-        <v>5800</v>
+        <v>14305</v>
       </c>
       <c r="H77" s="67">
         <v>300</v>
@@ -12806,7 +13028,7 @@
       </c>
       <c r="E78" s="57">
         <f>SUM($B$4:B78)+SUM($C$4:C78)-SUM($D$4:D78)</f>
-        <v>125200</v>
+        <v>97930</v>
       </c>
       <c r="F78" s="55">
         <f>SUM(经验!A78:X78)</f>
@@ -12814,7 +13036,7 @@
       </c>
       <c r="G78" s="55">
         <f>SUM($F$4:F78)+SUM($H$4:H78)</f>
-        <v>5800</v>
+        <v>14305</v>
       </c>
       <c r="H78" s="67">
         <v>0</v>
@@ -12929,7 +13151,7 @@
       </c>
       <c r="E79" s="57">
         <f>SUM($B$4:B79)+SUM($C$4:C79)-SUM($D$4:D79)</f>
-        <v>126800</v>
+        <v>99530</v>
       </c>
       <c r="F79" s="55">
         <f>SUM(经验!A79:X79)</f>
@@ -12937,7 +13159,7 @@
       </c>
       <c r="G79" s="55">
         <f>SUM($F$4:F79)+SUM($H$4:H79)</f>
-        <v>6000</v>
+        <v>14505</v>
       </c>
       <c r="H79" s="67">
         <v>200</v>
@@ -13052,7 +13274,7 @@
       </c>
       <c r="E80" s="57">
         <f>SUM($B$4:B80)+SUM($C$4:C80)-SUM($D$4:D80)</f>
-        <v>128400</v>
+        <v>101130</v>
       </c>
       <c r="F80" s="55">
         <f>SUM(经验!A80:X80)</f>
@@ -13060,7 +13282,7 @@
       </c>
       <c r="G80" s="55">
         <f>SUM($F$4:F80)+SUM($H$4:H80)</f>
-        <v>6000</v>
+        <v>14505</v>
       </c>
       <c r="H80" s="67">
         <v>0</v>
@@ -13175,7 +13397,7 @@
       </c>
       <c r="E81" s="57">
         <f>SUM($B$4:B81)+SUM($C$4:C81)-SUM($D$4:D81)</f>
-        <v>130000</v>
+        <v>102730</v>
       </c>
       <c r="F81" s="55">
         <f>SUM(经验!A81:X81)</f>
@@ -13183,7 +13405,7 @@
       </c>
       <c r="G81" s="55">
         <f>SUM($F$4:F81)+SUM($H$4:H81)</f>
-        <v>6000</v>
+        <v>14505</v>
       </c>
       <c r="H81" s="67">
         <v>0</v>
@@ -13298,7 +13520,7 @@
       </c>
       <c r="E82" s="57">
         <f>SUM($B$4:B82)+SUM($C$4:C82)-SUM($D$4:D82)</f>
-        <v>131600</v>
+        <v>104330</v>
       </c>
       <c r="F82" s="55">
         <f>SUM(经验!A82:X82)</f>
@@ -13306,7 +13528,7 @@
       </c>
       <c r="G82" s="55">
         <f>SUM($F$4:F82)+SUM($H$4:H82)</f>
-        <v>6000</v>
+        <v>14505</v>
       </c>
       <c r="H82" s="67">
         <v>0</v>
@@ -13421,7 +13643,7 @@
       </c>
       <c r="E83" s="57">
         <f>SUM($B$4:B83)+SUM($C$4:C83)-SUM($D$4:D83)</f>
-        <v>133200</v>
+        <v>105930</v>
       </c>
       <c r="F83" s="55">
         <f>SUM(经验!A83:X83)</f>
@@ -13429,7 +13651,7 @@
       </c>
       <c r="G83" s="55">
         <f>SUM($F$4:F83)+SUM($H$4:H83)</f>
-        <v>6000</v>
+        <v>14505</v>
       </c>
       <c r="H83" s="67">
         <v>0</v>
@@ -13544,7 +13766,7 @@
       </c>
       <c r="E84" s="57">
         <f>SUM($B$4:B84)+SUM($C$4:C84)-SUM($D$4:D84)</f>
-        <v>134800</v>
+        <v>107530</v>
       </c>
       <c r="F84" s="55">
         <f>SUM(经验!A84:X84)</f>
@@ -13552,7 +13774,7 @@
       </c>
       <c r="G84" s="55">
         <f>SUM($F$4:F84)+SUM($H$4:H84)</f>
-        <v>6200</v>
+        <v>14705</v>
       </c>
       <c r="H84" s="55">
         <v>200</v>
@@ -13667,7 +13889,7 @@
       </c>
       <c r="E85" s="57">
         <f>SUM($B$4:B85)+SUM($C$4:C85)-SUM($D$4:D85)</f>
-        <v>136400</v>
+        <v>109130</v>
       </c>
       <c r="F85" s="55">
         <f>SUM(经验!A85:X85)</f>
@@ -13675,7 +13897,7 @@
       </c>
       <c r="G85" s="55">
         <f>SUM($F$4:F85)+SUM($H$4:H85)</f>
-        <v>6200</v>
+        <v>14705</v>
       </c>
       <c r="H85" s="55">
         <v>0</v>
@@ -13790,7 +14012,7 @@
       </c>
       <c r="E86" s="57">
         <f>SUM($B$4:B86)+SUM($C$4:C86)-SUM($D$4:D86)</f>
-        <v>138000</v>
+        <v>110730</v>
       </c>
       <c r="F86" s="55">
         <f>SUM(经验!A86:X86)</f>
@@ -13798,7 +14020,7 @@
       </c>
       <c r="G86" s="55">
         <f>SUM($F$4:F86)+SUM($H$4:H86)</f>
-        <v>6500</v>
+        <v>15005</v>
       </c>
       <c r="H86" s="55">
         <v>300</v>
@@ -13913,7 +14135,7 @@
       </c>
       <c r="E87" s="57">
         <f>SUM($B$4:B87)+SUM($C$4:C87)-SUM($D$4:D87)</f>
-        <v>139600</v>
+        <v>112330</v>
       </c>
       <c r="F87" s="55">
         <f>SUM(经验!A87:X87)</f>
@@ -13921,7 +14143,7 @@
       </c>
       <c r="G87" s="55">
         <f>SUM($F$4:F87)+SUM($H$4:H87)</f>
-        <v>6500</v>
+        <v>15005</v>
       </c>
       <c r="H87" s="55">
         <v>0</v>
@@ -14036,7 +14258,7 @@
       </c>
       <c r="E88" s="57">
         <f>SUM($B$4:B88)+SUM($C$4:C88)-SUM($D$4:D88)</f>
-        <v>141200</v>
+        <v>113930</v>
       </c>
       <c r="F88" s="55">
         <f>SUM(经验!A88:X88)</f>
@@ -14044,7 +14266,7 @@
       </c>
       <c r="G88" s="55">
         <f>SUM($F$4:F88)+SUM($H$4:H88)</f>
-        <v>6500</v>
+        <v>15005</v>
       </c>
       <c r="H88" s="55">
         <v>0</v>
@@ -14159,7 +14381,7 @@
       </c>
       <c r="E89" s="57">
         <f>SUM($B$4:B89)+SUM($C$4:C89)-SUM($D$4:D89)</f>
-        <v>142800</v>
+        <v>115530</v>
       </c>
       <c r="F89" s="55">
         <f>SUM(经验!A89:X89)</f>
@@ -14167,7 +14389,7 @@
       </c>
       <c r="G89" s="55">
         <f>SUM($F$4:F89)+SUM($H$4:H89)</f>
-        <v>6500</v>
+        <v>15005</v>
       </c>
       <c r="H89" s="55">
         <v>0</v>
@@ -14282,7 +14504,7 @@
       </c>
       <c r="E90" s="57">
         <f>SUM($B$4:B90)+SUM($C$4:C90)-SUM($D$4:D90)</f>
-        <v>144400</v>
+        <v>117130</v>
       </c>
       <c r="F90" s="55">
         <f>SUM(经验!A90:X90)</f>
@@ -14290,7 +14512,7 @@
       </c>
       <c r="G90" s="55">
         <f>SUM($F$4:F90)+SUM($H$4:H90)</f>
-        <v>6500</v>
+        <v>15005</v>
       </c>
       <c r="H90" s="55">
         <v>0</v>
@@ -14405,7 +14627,7 @@
       </c>
       <c r="E91" s="57">
         <f>SUM($B$4:B91)+SUM($C$4:C91)-SUM($D$4:D91)</f>
-        <v>146000</v>
+        <v>118730</v>
       </c>
       <c r="F91" s="55">
         <f>SUM(经验!A91:X91)</f>
@@ -14413,7 +14635,7 @@
       </c>
       <c r="G91" s="55">
         <f>SUM($F$4:F91)+SUM($H$4:H91)</f>
-        <v>6700</v>
+        <v>15205</v>
       </c>
       <c r="H91" s="67">
         <v>200</v>
@@ -14528,7 +14750,7 @@
       </c>
       <c r="E92" s="57">
         <f>SUM($B$4:B92)+SUM($C$4:C92)-SUM($D$4:D92)</f>
-        <v>147600</v>
+        <v>120330</v>
       </c>
       <c r="F92" s="55">
         <f>SUM(经验!A92:X92)</f>
@@ -14536,7 +14758,7 @@
       </c>
       <c r="G92" s="55">
         <f>SUM($F$4:F92)+SUM($H$4:H92)</f>
-        <v>6800</v>
+        <v>15305</v>
       </c>
       <c r="H92" s="67">
         <v>100</v>
@@ -14650,7 +14872,7 @@
       </c>
       <c r="E93" s="57">
         <f>SUM($B$4:B93)+SUM($C$4:C93)-SUM($D$4:D93)</f>
-        <v>149200</v>
+        <v>121930</v>
       </c>
       <c r="F93" s="55">
         <f>SUM(经验!A93:X93)</f>
@@ -14658,7 +14880,7 @@
       </c>
       <c r="G93" s="89">
         <f>SUM($F$4:F93)+SUM($H$4:H93)</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="H93">
         <v>200</v>
@@ -14772,7 +14994,7 @@
       </c>
       <c r="E94" s="57">
         <f>SUM($B$4:B94)+SUM($C$4:C94)-SUM($D$4:D94)</f>
-        <v>150800</v>
+        <v>123530</v>
       </c>
       <c r="F94" s="55">
         <f>SUM(经验!A94:X94)</f>
@@ -14780,7 +15002,7 @@
       </c>
       <c r="G94" s="89">
         <f>SUM($F$4:F94)+SUM($H$4:H94)</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -14868,15 +15090,15 @@
         <v>57</v>
       </c>
       <c r="AL94" s="64">
-        <f t="shared" ref="AL94:AL101" si="38">MIN(AL93+6,18)-COUNTIF(I94:P94,"&lt;&gt;空")+COUNTIF(I94:P94,"历练")+COUNTIF(I94:P94,"营地")*2+COUNTIF(I94:P94,"塔1")*5</f>
+        <f t="shared" ref="AL94:AL100" si="38">MIN(AL93+6,18)-COUNTIF(I94:P94,"&lt;&gt;空")+COUNTIF(I94:P94,"历练")+COUNTIF(I94:P94,"营地")*2+COUNTIF(I94:P94,"塔1")*5</f>
         <v>18</v>
       </c>
       <c r="AM94" s="64">
-        <f t="shared" ref="AM94:AM101" si="39">MIN(AM93+6,18)-COUNTIF(Q94:X94,"&lt;&gt;空")+COUNTIF(Q94:X94,"历练")+COUNTIF(Q94:X94,"营地")*2+COUNTIF(Q94:X94,"塔1")*5</f>
+        <f t="shared" ref="AM94:AM100" si="39">MIN(AM93+6,18)-COUNTIF(Q94:X94,"&lt;&gt;空")+COUNTIF(Q94:X94,"历练")+COUNTIF(Q94:X94,"营地")*2+COUNTIF(Q94:X94,"塔1")*5</f>
         <v>18</v>
       </c>
       <c r="AN94" s="64">
-        <f t="shared" ref="AN94:AN101" si="40">MIN(AN93+6,18)-COUNTIF(Y94:AF94,"&lt;&gt;空")+COUNTIF(Y94:AF94,"历练")+COUNTIF(Y94:AF94,"营地")*2+COUNTIF(Y94:AF94,"塔1")*5</f>
+        <f t="shared" ref="AN94:AN100" si="40">MIN(AN93+6,18)-COUNTIF(Y94:AF94,"&lt;&gt;空")+COUNTIF(Y94:AF94,"历练")+COUNTIF(Y94:AF94,"营地")*2+COUNTIF(Y94:AF94,"塔1")*5</f>
         <v>18</v>
       </c>
     </row>
@@ -14893,7 +15115,7 @@
       </c>
       <c r="E95" s="57">
         <f>SUM($B$4:B95)+SUM($C$4:C95)-SUM($D$4:D95)</f>
-        <v>152400</v>
+        <v>125130</v>
       </c>
       <c r="F95" s="55">
         <f>SUM(经验!A95:X95)</f>
@@ -14901,7 +15123,7 @@
       </c>
       <c r="G95" s="89">
         <f>SUM($F$4:F95)+SUM($H$4:H95)</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -15014,7 +15236,7 @@
       </c>
       <c r="E96" s="57">
         <f>SUM($B$4:B96)+SUM($C$4:C96)-SUM($D$4:D96)</f>
-        <v>154000</v>
+        <v>126730</v>
       </c>
       <c r="F96" s="55">
         <f>SUM(经验!A96:X96)</f>
@@ -15022,7 +15244,7 @@
       </c>
       <c r="G96" s="89">
         <f>SUM($F$4:F96)+SUM($H$4:H96)</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -15135,7 +15357,7 @@
       </c>
       <c r="E97" s="57">
         <f>SUM($B$4:B97)+SUM($C$4:C97)-SUM($D$4:D97)</f>
-        <v>155600</v>
+        <v>128330</v>
       </c>
       <c r="F97" s="55">
         <f>SUM(经验!A97:X97)</f>
@@ -15143,7 +15365,7 @@
       </c>
       <c r="G97" s="89">
         <f>SUM($F$4:F97)+SUM($H$4:H97)</f>
-        <v>7000</v>
+        <v>15505</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -15247,7 +15469,7 @@
       <c r="A98" s="95">
         <v>46370</v>
       </c>
-      <c r="B98" s="138">
+      <c r="B98" s="102">
         <v>1600</v>
       </c>
       <c r="D98" s="55">
@@ -15256,7 +15478,7 @@
       </c>
       <c r="E98" s="57">
         <f>SUM($B$4:B98)+SUM($C$4:C98)-SUM($D$4:D98)</f>
-        <v>157200</v>
+        <v>129930</v>
       </c>
       <c r="F98" s="55">
         <f>SUM(经验!A98:X98)</f>
@@ -15264,7 +15486,7 @@
       </c>
       <c r="G98" s="89">
         <f>SUM($F$4:F98)+SUM($H$4:H98)</f>
-        <v>7200</v>
+        <v>15705</v>
       </c>
       <c r="H98" s="67">
         <v>200</v>
@@ -15368,7 +15590,7 @@
       <c r="A99" s="95">
         <v>46371</v>
       </c>
-      <c r="B99" s="138">
+      <c r="B99" s="102">
         <v>1600</v>
       </c>
       <c r="D99" s="55">
@@ -15377,7 +15599,7 @@
       </c>
       <c r="E99" s="57">
         <f>SUM($B$4:B99)+SUM($C$4:C99)-SUM($D$4:D99)</f>
-        <v>158800</v>
+        <v>131530</v>
       </c>
       <c r="F99" s="55">
         <f>SUM(经验!A99:X99)</f>
@@ -15385,7 +15607,7 @@
       </c>
       <c r="G99" s="89">
         <f>SUM($F$4:F99)+SUM($H$4:H99)</f>
-        <v>7300</v>
+        <v>15805</v>
       </c>
       <c r="H99" s="67">
         <v>100</v>
@@ -15489,7 +15711,7 @@
       <c r="A100" s="95">
         <v>46372</v>
       </c>
-      <c r="B100" s="138">
+      <c r="B100" s="102">
         <v>1600</v>
       </c>
       <c r="D100" s="55">
@@ -15498,7 +15720,7 @@
       </c>
       <c r="E100" s="57">
         <f>SUM($B$4:B100)+SUM($C$4:C100)-SUM($D$4:D100)</f>
-        <v>160400</v>
+        <v>133130</v>
       </c>
       <c r="F100" s="55">
         <f>SUM(经验!A100:X100)</f>
@@ -15506,7 +15728,7 @@
       </c>
       <c r="G100" s="89">
         <f>SUM($F$4:F100)+SUM($H$4:H100)</f>
-        <v>7500</v>
+        <v>16005</v>
       </c>
       <c r="H100">
         <v>200</v>
@@ -15684,10 +15906,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="128" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="128"/>
+      <c r="C1" s="129"/>
       <c r="D1" s="14"/>
       <c r="E1" s="14"/>
       <c r="F1" s="14"/>
@@ -15898,10 +16120,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="132"/>
+      <c r="B2" s="133"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -15909,16 +16131,16 @@
         <f>COUNTIF(A4:H94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="135"/>
+      <c r="J2" s="136"/>
       <c r="K2" s="2" t="s">
         <v>3</v>
       </c>
@@ -15926,16 +16148,16 @@
         <f>COUNTIF(I4:P94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="M2" s="135" t="s">
+      <c r="M2" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="137" t="s">
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="129"/>
+      <c r="R2" s="130"/>
       <c r="S2" s="4" t="s">
         <v>7</v>
       </c>
@@ -15943,12 +16165,12 @@
         <f>COUNTIF(Q4:X94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="U2" s="129" t="s">
+      <c r="U2" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="130"/>
+      <c r="V2" s="130"/>
+      <c r="W2" s="130"/>
+      <c r="X2" s="131"/>
       <c r="Y2" t="s">
         <v>15</v>
       </c>
@@ -16033,27 +16255,27 @@
     <row r="4" spans="1:27">
       <c r="A4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="B4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
@@ -16065,27 +16287,27 @@
       </c>
       <c r="I4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O4" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W4)),(-$Y4+50*IF(main!$AK4="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W4,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK4="是",main!$BB$4,main!$BB$3))</f>
@@ -16140,27 +16362,27 @@
     <row r="5" spans="1:27">
       <c r="A5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="B5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
@@ -16172,27 +16394,27 @@
       </c>
       <c r="I5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O5" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W5)),(-$Y5+50*IF(main!$AK5="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W5,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK5="是",main!$BB$4,main!$BB$3))</f>
@@ -16247,27 +16469,27 @@
     <row r="6" spans="1:27">
       <c r="A6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="B6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="C6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
@@ -16279,23 +16501,23 @@
       </c>
       <c r="I6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="J6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="K6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N6" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V6)),(-$Y6+50*IF(main!$AK6="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V6,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK6="是",main!$BB$4,main!$BB$3))</f>
@@ -16354,31 +16576,31 @@
     <row r="7" spans="1:27">
       <c r="A7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="B7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
@@ -16386,35 +16608,35 @@
       </c>
       <c r="I7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!X7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!X7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Q7" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Y7)),(-$Y7+50*IF(main!$AK7="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Y7,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK7="是",main!$BB$4,main!$BB$3))</f>
@@ -16461,63 +16683,63 @@
     <row r="8" spans="1:27">
       <c r="A8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P8" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!X8)),(-$Y8+50*IF(main!$AK8="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!X8,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK8="是",main!$BB$4,main!$BB$3))</f>
@@ -16568,43 +16790,43 @@
     <row r="9" spans="1:27">
       <c r="A9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="J9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="K9" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S9)),(-$Y9+50*IF(main!$AK9="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S9,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK9="是",main!$BB$4,main!$BB$3))</f>
@@ -16675,47 +16897,47 @@
     <row r="10" spans="1:27">
       <c r="A10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="J10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L10" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T10)),(-$Y10+50*IF(main!$AK10="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T10,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK10="是",main!$BB$4,main!$BB$3))</f>
@@ -16782,55 +17004,55 @@
     <row r="11" spans="1:27">
       <c r="A11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="J11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="M11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="N11" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V11)),(-$Y11+50*IF(main!$AK11="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V11,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK11="是",main!$BB$4,main!$BB$3))</f>
@@ -16889,67 +17111,67 @@
     <row r="12" spans="1:27">
       <c r="A12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="J12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="M12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="N12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="O12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="P12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!X12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!X12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="Q12" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Y12)),(-$Y12+50*IF(main!$AK12="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Y12,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK12="是",main!$BB$4,main!$BB$3))</f>
@@ -16996,35 +17218,35 @@
     <row r="13" spans="1:27">
       <c r="A13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I13" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q13)),(-$Y13+50*IF(main!$AK13="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q13,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK13="是",main!$BB$4,main!$BB$3))</f>
@@ -17103,35 +17325,35 @@
     <row r="14" spans="1:27">
       <c r="A14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I14" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q14)),(-$Y14+50*IF(main!$AK14="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q14,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK14="是",main!$BB$4,main!$BB$3))</f>
@@ -17210,35 +17432,35 @@
     <row r="15" spans="1:27">
       <c r="A15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="B15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="F15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="H15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="I15" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q15)),(-$Y15+50*IF(main!$AK15="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q15,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK15="是",main!$BB$4,main!$BB$3))</f>
@@ -17317,95 +17539,95 @@
     <row r="16" spans="1:27">
       <c r="A16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="B16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="D16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="F16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!X16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!X16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Y16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Y16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Z16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Z16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AA16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AA16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AB16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AB16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AC16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AC16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AD16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AD16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AE16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AE16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="X16" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AF16)),(-$Y16+50*IF(main!$AK16="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AF16,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK16="是",main!$BB$4,main!$BB$3))</f>
@@ -17424,99 +17646,99 @@
     <row r="17" spans="1:27">
       <c r="A17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!I17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!I17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="B17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!J17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!J17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!K17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!K17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="D17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!L17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!L17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!M17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!M17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="F17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!N17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!N17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="G17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!O17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!O17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!P17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!P17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="I17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Q17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Q17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="J17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!R17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!R17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!S17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!S17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="L17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!T17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!T17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!U17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!U17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!V17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!V17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="O17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!W17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!W17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="P17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!X17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!X17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="Q17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Y17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Y17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="R17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!Z17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!Z17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="S17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AA17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AA17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="T17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AB17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AB17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="U17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AC17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AC17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="V17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AD17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AD17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="W17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AE17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AE17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="X17" s="12">
         <f>IF(ISNUMBER(SEARCH("营",main!AF17)),(-$Y17+50*IF(main!$AK17="是",main!$BB$4,main!$BB$3)),(VLOOKUP(main!AF17,main!$AO$4:$AQ$55,2,FALSE))*IF(main!$AK17="是",main!$BB$4,main!$BB$3))</f>
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="Y17" s="94">
         <v>300</v>
@@ -26430,10 +26652,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:24">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="132"/>
+      <c r="B2" s="133"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -26441,16 +26663,16 @@
         <f>COUNTIF(A4:H94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="135"/>
+      <c r="J2" s="136"/>
       <c r="K2" s="2" t="s">
         <v>3</v>
       </c>
@@ -26458,16 +26680,16 @@
         <f>COUNTIF(I4:P94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="M2" s="135" t="s">
+      <c r="M2" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="137" t="s">
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="129"/>
+      <c r="R2" s="130"/>
       <c r="S2" s="4" t="s">
         <v>7</v>
       </c>
@@ -26475,12 +26697,12 @@
         <f>COUNTIF(Q4:X94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="U2" s="129" t="s">
+      <c r="U2" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="130"/>
+      <c r="V2" s="130"/>
+      <c r="W2" s="130"/>
+      <c r="X2" s="131"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="5">
@@ -26559,27 +26781,27 @@
     <row r="4" spans="1:24">
       <c r="A4" s="12">
         <f>(VLOOKUP(main!I4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B4" s="12">
         <f>(VLOOKUP(main!J4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C4" s="12">
         <f>(VLOOKUP(main!K4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <f>(VLOOKUP(main!L4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E4" s="12">
         <f>(VLOOKUP(main!M4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F4" s="12">
         <f>(VLOOKUP(main!N4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4" s="13">
         <f>(VLOOKUP(main!O4,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26591,27 +26813,27 @@
       </c>
       <c r="I4" s="12">
         <f>(VLOOKUP(main!Q4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J4" s="12">
         <f>(VLOOKUP(main!R4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K4" s="12">
         <f>(VLOOKUP(main!S4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L4" s="12">
         <f>(VLOOKUP(main!T4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M4" s="12">
         <f>(VLOOKUP(main!U4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N4" s="12">
         <f>(VLOOKUP(main!V4,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O4" s="13">
         <f>(VLOOKUP(main!W4,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26657,27 +26879,27 @@
     <row r="5" spans="1:24">
       <c r="A5" s="12">
         <f>(VLOOKUP(main!I5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B5" s="12">
         <f>(VLOOKUP(main!J5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C5" s="12">
         <f>(VLOOKUP(main!K5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D5" s="12">
         <f>(VLOOKUP(main!L5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E5" s="12">
         <f>(VLOOKUP(main!M5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5" s="12">
         <f>(VLOOKUP(main!N5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5" s="13">
         <f>(VLOOKUP(main!O5,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26689,27 +26911,27 @@
       </c>
       <c r="I5" s="12">
         <f>(VLOOKUP(main!Q5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J5" s="12">
         <f>(VLOOKUP(main!R5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K5" s="12">
         <f>(VLOOKUP(main!S5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L5" s="12">
         <f>(VLOOKUP(main!T5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M5" s="12">
         <f>(VLOOKUP(main!U5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N5" s="12">
         <f>(VLOOKUP(main!V5,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O5" s="13">
         <f>(VLOOKUP(main!W5,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26755,27 +26977,27 @@
     <row r="6" spans="1:24">
       <c r="A6" s="12">
         <f>(VLOOKUP(main!I6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B6" s="12">
         <f>(VLOOKUP(main!J6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C6" s="12">
         <f>(VLOOKUP(main!K6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D6" s="12">
         <f>(VLOOKUP(main!L6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E6" s="12">
         <f>(VLOOKUP(main!M6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F6" s="12">
         <f>(VLOOKUP(main!N6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6" s="13">
         <f>(VLOOKUP(main!O6,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26787,23 +27009,23 @@
       </c>
       <c r="I6" s="12">
         <f>(VLOOKUP(main!Q6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J6" s="12">
         <f>(VLOOKUP(main!R6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K6" s="12">
         <f>(VLOOKUP(main!S6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L6" s="12">
         <f>(VLOOKUP(main!T6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M6" s="12">
         <f>(VLOOKUP(main!U6,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N6" s="12">
         <f>(VLOOKUP(main!V6,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26853,31 +27075,31 @@
     <row r="7" spans="1:24">
       <c r="A7" s="12">
         <f>(VLOOKUP(main!I7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B7" s="12">
         <f>(VLOOKUP(main!J7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C7" s="12">
         <f>(VLOOKUP(main!K7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D7" s="12">
         <f>(VLOOKUP(main!L7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E7" s="12">
         <f>(VLOOKUP(main!M7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F7" s="12">
         <f>(VLOOKUP(main!N7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G7" s="13">
         <f>(VLOOKUP(main!O7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H7" s="13">
         <f>(VLOOKUP(main!P7,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26885,35 +27107,35 @@
       </c>
       <c r="I7" s="12">
         <f>(VLOOKUP(main!Q7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J7" s="12">
         <f>(VLOOKUP(main!R7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K7" s="12">
         <f>(VLOOKUP(main!S7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L7" s="12">
         <f>(VLOOKUP(main!T7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M7" s="12">
         <f>(VLOOKUP(main!U7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N7" s="12">
         <f>(VLOOKUP(main!V7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O7" s="13">
         <f>(VLOOKUP(main!W7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P7" s="13">
         <f>(VLOOKUP(main!X7,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="12">
         <f>(VLOOKUP(main!Y7,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -26951,63 +27173,63 @@
     <row r="8" spans="1:24">
       <c r="A8" s="12">
         <f>(VLOOKUP(main!I8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B8" s="12">
         <f>(VLOOKUP(main!J8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C8" s="12">
         <f>(VLOOKUP(main!K8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D8" s="12">
         <f>(VLOOKUP(main!L8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E8" s="12">
         <f>(VLOOKUP(main!M8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F8" s="12">
         <f>(VLOOKUP(main!N8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G8" s="13">
         <f>(VLOOKUP(main!O8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H8" s="13">
         <f>(VLOOKUP(main!P8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I8" s="12">
         <f>(VLOOKUP(main!Q8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J8" s="12">
         <f>(VLOOKUP(main!R8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K8" s="12">
         <f>(VLOOKUP(main!S8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L8" s="12">
         <f>(VLOOKUP(main!T8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M8" s="12">
         <f>(VLOOKUP(main!U8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N8" s="12">
         <f>(VLOOKUP(main!V8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O8" s="13">
         <f>(VLOOKUP(main!W8,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P8" s="13">
         <f>(VLOOKUP(main!X8,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27049,35 +27271,35 @@
     <row r="9" spans="1:24">
       <c r="A9" s="12">
         <f>(VLOOKUP(main!I9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B9" s="12">
         <f>(VLOOKUP(main!J9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C9" s="12">
         <f>(VLOOKUP(main!K9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D9" s="12">
         <f>(VLOOKUP(main!L9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E9" s="12">
         <f>(VLOOKUP(main!M9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F9" s="12">
         <f>(VLOOKUP(main!N9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G9" s="13">
         <f>(VLOOKUP(main!O9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H9" s="13">
         <f>(VLOOKUP(main!P9,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I9" s="12">
         <f>(VLOOKUP(main!Q9,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27147,47 +27369,47 @@
     <row r="10" spans="1:24">
       <c r="A10" s="12">
         <f>(VLOOKUP(main!I10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B10" s="12">
         <f>(VLOOKUP(main!J10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C10" s="12">
         <f>(VLOOKUP(main!K10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D10" s="12">
         <f>(VLOOKUP(main!L10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E10" s="12">
         <f>(VLOOKUP(main!M10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F10" s="12">
         <f>(VLOOKUP(main!N10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G10" s="13">
         <f>(VLOOKUP(main!O10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H10" s="13">
         <f>(VLOOKUP(main!P10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I10" s="12">
         <f>(VLOOKUP(main!Q10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J10" s="12">
         <f>(VLOOKUP(main!R10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K10" s="12">
         <f>(VLOOKUP(main!S10,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L10" s="12">
         <f>(VLOOKUP(main!T10,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27245,55 +27467,55 @@
     <row r="11" spans="1:24">
       <c r="A11" s="12">
         <f>(VLOOKUP(main!I11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B11" s="12">
         <f>(VLOOKUP(main!J11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C11" s="12">
         <f>(VLOOKUP(main!K11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D11" s="12">
         <f>(VLOOKUP(main!L11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E11" s="12">
         <f>(VLOOKUP(main!M11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F11" s="12">
         <f>(VLOOKUP(main!N11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G11" s="13">
         <f>(VLOOKUP(main!O11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H11" s="13">
         <f>(VLOOKUP(main!P11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I11" s="12">
         <f>(VLOOKUP(main!Q11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J11" s="12">
         <f>(VLOOKUP(main!R11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K11" s="12">
         <f>(VLOOKUP(main!S11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L11" s="12">
         <f>(VLOOKUP(main!T11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M11" s="12">
         <f>(VLOOKUP(main!U11,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N11" s="12">
         <f>(VLOOKUP(main!V11,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27343,67 +27565,67 @@
     <row r="12" spans="1:24">
       <c r="A12" s="12">
         <f>(VLOOKUP(main!I12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B12" s="12">
         <f>(VLOOKUP(main!J12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C12" s="12">
         <f>(VLOOKUP(main!K12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D12" s="12">
         <f>(VLOOKUP(main!L12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E12" s="12">
         <f>(VLOOKUP(main!M12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F12" s="12">
         <f>(VLOOKUP(main!N12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" s="13">
         <f>(VLOOKUP(main!O12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H12" s="13">
         <f>(VLOOKUP(main!P12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I12" s="12">
         <f>(VLOOKUP(main!Q12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J12" s="12">
         <f>(VLOOKUP(main!R12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K12" s="12">
         <f>(VLOOKUP(main!S12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12">
         <f>(VLOOKUP(main!T12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M12" s="12">
         <f>(VLOOKUP(main!U12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N12" s="12">
         <f>(VLOOKUP(main!V12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O12" s="13">
         <f>(VLOOKUP(main!W12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P12" s="13">
         <f>(VLOOKUP(main!X12,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q12" s="12">
         <f>(VLOOKUP(main!Y12,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27441,35 +27663,35 @@
     <row r="13" spans="1:24">
       <c r="A13" s="12">
         <f>(VLOOKUP(main!I13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B13" s="12">
         <f>(VLOOKUP(main!J13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C13" s="12">
         <f>(VLOOKUP(main!K13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D13" s="12">
         <f>(VLOOKUP(main!L13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E13" s="12">
         <f>(VLOOKUP(main!M13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F13" s="12">
         <f>(VLOOKUP(main!N13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G13" s="13">
         <f>(VLOOKUP(main!O13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H13" s="13">
         <f>(VLOOKUP(main!P13,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I13" s="12">
         <f>(VLOOKUP(main!Q13,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27539,35 +27761,35 @@
     <row r="14" spans="1:24">
       <c r="A14" s="12">
         <f>(VLOOKUP(main!I14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B14" s="12">
         <f>(VLOOKUP(main!J14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C14" s="12">
         <f>(VLOOKUP(main!K14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D14" s="12">
         <f>(VLOOKUP(main!L14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E14" s="12">
         <f>(VLOOKUP(main!M14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F14" s="12">
         <f>(VLOOKUP(main!N14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G14" s="13">
         <f>(VLOOKUP(main!O14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H14" s="13">
         <f>(VLOOKUP(main!P14,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I14" s="12">
         <f>(VLOOKUP(main!Q14,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27637,35 +27859,35 @@
     <row r="15" spans="1:24">
       <c r="A15" s="12">
         <f>(VLOOKUP(main!I15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B15" s="12">
         <f>(VLOOKUP(main!J15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C15" s="12">
         <f>(VLOOKUP(main!K15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D15" s="12">
         <f>(VLOOKUP(main!L15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E15" s="12">
         <f>(VLOOKUP(main!M15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F15" s="12">
         <f>(VLOOKUP(main!N15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G15" s="13">
         <f>(VLOOKUP(main!O15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H15" s="13">
         <f>(VLOOKUP(main!P15,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I15" s="12">
         <f>(VLOOKUP(main!Q15,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27735,91 +27957,91 @@
     <row r="16" spans="1:24">
       <c r="A16" s="12">
         <f>(VLOOKUP(main!I16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B16" s="12">
         <f>(VLOOKUP(main!J16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C16" s="12">
         <f>(VLOOKUP(main!K16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D16" s="12">
         <f>(VLOOKUP(main!L16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E16" s="12">
         <f>(VLOOKUP(main!M16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F16" s="12">
         <f>(VLOOKUP(main!N16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G16" s="13">
         <f>(VLOOKUP(main!O16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H16" s="13">
         <f>(VLOOKUP(main!P16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I16" s="12">
         <f>(VLOOKUP(main!Q16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J16" s="12">
         <f>(VLOOKUP(main!R16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K16" s="12">
         <f>(VLOOKUP(main!S16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L16" s="12">
         <f>(VLOOKUP(main!T16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M16" s="12">
         <f>(VLOOKUP(main!U16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N16" s="12">
         <f>(VLOOKUP(main!V16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O16" s="13">
         <f>(VLOOKUP(main!W16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P16" s="13">
         <f>(VLOOKUP(main!X16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q16" s="12">
         <f>(VLOOKUP(main!Y16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="R16" s="12">
         <f>(VLOOKUP(main!Z16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S16" s="12">
         <f>(VLOOKUP(main!AA16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T16" s="12">
         <f>(VLOOKUP(main!AB16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U16" s="12">
         <f>(VLOOKUP(main!AC16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V16" s="12">
         <f>(VLOOKUP(main!AD16,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W16" s="13">
         <f>(VLOOKUP(main!AE16,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27833,55 +28055,55 @@
     <row r="17" spans="1:24">
       <c r="A17" s="12">
         <f>(VLOOKUP(main!I17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B17" s="12">
         <f>(VLOOKUP(main!J17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C17" s="12">
         <f>(VLOOKUP(main!K17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D17" s="12">
         <f>(VLOOKUP(main!L17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E17" s="12">
         <f>(VLOOKUP(main!M17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F17" s="12">
         <f>(VLOOKUP(main!N17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G17" s="13">
         <f>(VLOOKUP(main!O17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H17" s="13">
         <f>(VLOOKUP(main!P17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12">
         <f>(VLOOKUP(main!Q17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J17" s="12">
         <f>(VLOOKUP(main!R17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K17" s="12">
         <f>(VLOOKUP(main!S17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L17" s="12">
         <f>(VLOOKUP(main!T17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M17" s="12">
         <f>(VLOOKUP(main!U17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N17" s="12">
         <f>(VLOOKUP(main!V17,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -27889,39 +28111,39 @@
       </c>
       <c r="O17" s="13">
         <f>(VLOOKUP(main!W17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="P17" s="13">
         <f>(VLOOKUP(main!X17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q17" s="12">
         <f>(VLOOKUP(main!Y17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R17" s="12">
         <f>(VLOOKUP(main!Z17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S17" s="12">
         <f>(VLOOKUP(main!AA17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="T17" s="12">
         <f>(VLOOKUP(main!AB17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="U17" s="12">
         <f>(VLOOKUP(main!AC17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V17" s="12">
         <f>(VLOOKUP(main!AD17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W17" s="13">
         <f>(VLOOKUP(main!AE17,main!$AO$4:$AQ$55,3,FALSE))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="X17" s="13">
         <f>(VLOOKUP(main!AF17,main!$AO$4:$AQ$55,3,FALSE))</f>
@@ -35423,10 +35645,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:24">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="132"/>
+      <c r="B2" s="133"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -35434,16 +35656,16 @@
         <f>COUNTIF(A4:H94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134" t="s">
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="135"/>
+      <c r="J2" s="136"/>
       <c r="K2" s="2" t="s">
         <v>3</v>
       </c>
@@ -35451,16 +35673,16 @@
         <f>COUNTIF(I4:P94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="M2" s="135" t="s">
+      <c r="M2" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="135"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="137" t="s">
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="129"/>
+      <c r="R2" s="130"/>
       <c r="S2" s="4" t="s">
         <v>7</v>
       </c>
@@ -35468,12 +35690,12 @@
         <f>COUNTIF(Q4:X94,"&lt;&gt;空")</f>
         <v>728</v>
       </c>
-      <c r="U2" s="129" t="s">
+      <c r="U2" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="130"/>
+      <c r="V2" s="130"/>
+      <c r="W2" s="130"/>
+      <c r="X2" s="131"/>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="5">
@@ -35552,27 +35774,27 @@
     <row r="4" spans="1:24">
       <c r="A4" s="12">
         <f>(VLOOKUP(main!I4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="B4" s="12">
         <f>(VLOOKUP(main!J4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="C4" s="12">
         <f>(VLOOKUP(main!K4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="D4" s="12">
         <f>(VLOOKUP(main!L4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="E4" s="12">
         <f>(VLOOKUP(main!M4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="F4" s="12">
         <f>(VLOOKUP(main!N4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="G4" s="12">
         <f>(VLOOKUP(main!O4,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35584,27 +35806,27 @@
       </c>
       <c r="I4" s="12">
         <f>(VLOOKUP(main!Q4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J4" s="12">
         <f>(VLOOKUP(main!R4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K4" s="12">
         <f>(VLOOKUP(main!S4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L4" s="12">
         <f>(VLOOKUP(main!T4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M4" s="12">
         <f>(VLOOKUP(main!U4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N4" s="12">
         <f>(VLOOKUP(main!V4,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O4" s="12">
         <f>(VLOOKUP(main!W4,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35650,27 +35872,27 @@
     <row r="5" spans="1:24">
       <c r="A5" s="12">
         <f>(VLOOKUP(main!I5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="B5" s="12">
         <f>(VLOOKUP(main!J5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="C5" s="12">
         <f>(VLOOKUP(main!K5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="D5" s="12">
         <f>(VLOOKUP(main!L5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="E5" s="12">
         <f>(VLOOKUP(main!M5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="F5" s="12">
         <f>(VLOOKUP(main!N5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="G5" s="12">
         <f>(VLOOKUP(main!O5,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35682,27 +35904,27 @@
       </c>
       <c r="I5" s="12">
         <f>(VLOOKUP(main!Q5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J5" s="12">
         <f>(VLOOKUP(main!R5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K5" s="12">
         <f>(VLOOKUP(main!S5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L5" s="12">
         <f>(VLOOKUP(main!T5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M5" s="12">
         <f>(VLOOKUP(main!U5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N5" s="12">
         <f>(VLOOKUP(main!V5,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O5" s="12">
         <f>(VLOOKUP(main!W5,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35748,27 +35970,27 @@
     <row r="6" spans="1:24">
       <c r="A6" s="12">
         <f>(VLOOKUP(main!I6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="B6" s="12">
         <f>(VLOOKUP(main!J6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="C6" s="12">
         <f>(VLOOKUP(main!K6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="D6" s="12">
         <f>(VLOOKUP(main!L6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="E6" s="12">
         <f>(VLOOKUP(main!M6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="F6" s="12">
         <f>(VLOOKUP(main!N6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="G6" s="12">
         <f>(VLOOKUP(main!O6,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35780,23 +36002,23 @@
       </c>
       <c r="I6" s="12">
         <f>(VLOOKUP(main!Q6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J6" s="12">
         <f>(VLOOKUP(main!R6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K6" s="12">
         <f>(VLOOKUP(main!S6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L6" s="12">
         <f>(VLOOKUP(main!T6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="M6" s="12">
         <f>(VLOOKUP(main!U6,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>13.9998549331786</v>
       </c>
       <c r="N6" s="12">
         <f>(VLOOKUP(main!V6,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35846,31 +36068,31 @@
     <row r="7" spans="1:24">
       <c r="A7" s="12">
         <f>(VLOOKUP(main!I7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="B7" s="12">
         <f>(VLOOKUP(main!J7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C7" s="12">
         <f>(VLOOKUP(main!K7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D7" s="12">
         <f>(VLOOKUP(main!L7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E7" s="12">
         <f>(VLOOKUP(main!M7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F7" s="12">
         <f>(VLOOKUP(main!N7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G7" s="12">
         <f>(VLOOKUP(main!O7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H7" s="12">
         <f>(VLOOKUP(main!P7,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35878,35 +36100,35 @@
       </c>
       <c r="I7" s="12">
         <f>(VLOOKUP(main!Q7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="J7" s="12">
         <f>(VLOOKUP(main!R7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="K7" s="12">
         <f>(VLOOKUP(main!S7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="L7" s="12">
         <f>(VLOOKUP(main!T7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="M7" s="12">
         <f>(VLOOKUP(main!U7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="N7" s="12">
         <f>(VLOOKUP(main!V7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="O7" s="12">
         <f>(VLOOKUP(main!W7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="P7" s="12">
         <f>(VLOOKUP(main!X7,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="Q7" s="12">
         <f>(VLOOKUP(main!Y7,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -35944,63 +36166,63 @@
     <row r="8" spans="1:24">
       <c r="A8" s="12">
         <f>(VLOOKUP(main!I8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B8" s="12">
         <f>(VLOOKUP(main!J8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C8" s="12">
         <f>(VLOOKUP(main!K8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D8" s="12">
         <f>(VLOOKUP(main!L8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E8" s="12">
         <f>(VLOOKUP(main!M8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8" s="12">
         <f>(VLOOKUP(main!N8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G8" s="12">
         <f>(VLOOKUP(main!O8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H8" s="12">
         <f>(VLOOKUP(main!P8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I8" s="12">
         <f>(VLOOKUP(main!Q8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J8" s="12">
         <f>(VLOOKUP(main!R8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K8" s="12">
         <f>(VLOOKUP(main!S8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" s="12">
         <f>(VLOOKUP(main!T8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M8" s="12">
         <f>(VLOOKUP(main!U8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N8" s="12">
         <f>(VLOOKUP(main!V8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" s="12">
         <f>(VLOOKUP(main!W8,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P8" s="12">
         <f>(VLOOKUP(main!X8,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36042,43 +36264,43 @@
     <row r="9" spans="1:24">
       <c r="A9" s="12">
         <f>(VLOOKUP(main!I9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B9" s="12">
         <f>(VLOOKUP(main!J9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C9" s="12">
         <f>(VLOOKUP(main!K9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D9" s="12">
         <f>(VLOOKUP(main!L9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E9" s="12">
         <f>(VLOOKUP(main!M9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9" s="12">
         <f>(VLOOKUP(main!N9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G9" s="12">
         <f>(VLOOKUP(main!O9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H9" s="12">
         <f>(VLOOKUP(main!P9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I9" s="12">
         <f>(VLOOKUP(main!Q9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" s="12">
         <f>(VLOOKUP(main!R9,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K9" s="12">
         <f>(VLOOKUP(main!S9,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36140,35 +36362,35 @@
     <row r="10" spans="1:24">
       <c r="A10" s="12">
         <f>(VLOOKUP(main!I10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B10" s="12">
         <f>(VLOOKUP(main!J10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C10" s="12">
         <f>(VLOOKUP(main!K10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D10" s="12">
         <f>(VLOOKUP(main!L10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E10" s="12">
         <f>(VLOOKUP(main!M10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F10" s="12">
         <f>(VLOOKUP(main!N10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G10" s="12">
         <f>(VLOOKUP(main!O10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H10" s="12">
         <f>(VLOOKUP(main!P10,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I10" s="12">
         <f>(VLOOKUP(main!Q10,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36238,35 +36460,35 @@
     <row r="11" spans="1:24">
       <c r="A11" s="12">
         <f>(VLOOKUP(main!I11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B11" s="12">
         <f>(VLOOKUP(main!J11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C11" s="12">
         <f>(VLOOKUP(main!K11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D11" s="12">
         <f>(VLOOKUP(main!L11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E11" s="12">
         <f>(VLOOKUP(main!M11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F11" s="12">
         <f>(VLOOKUP(main!N11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G11" s="12">
         <f>(VLOOKUP(main!O11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H11" s="12">
         <f>(VLOOKUP(main!P11,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I11" s="12">
         <f>(VLOOKUP(main!Q11,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36336,67 +36558,67 @@
     <row r="12" spans="1:24">
       <c r="A12" s="12">
         <f>(VLOOKUP(main!I12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B12" s="12">
         <f>(VLOOKUP(main!J12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C12" s="12">
         <f>(VLOOKUP(main!K12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D12" s="12">
         <f>(VLOOKUP(main!L12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E12" s="12">
         <f>(VLOOKUP(main!M12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F12" s="12">
         <f>(VLOOKUP(main!N12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G12" s="12">
         <f>(VLOOKUP(main!O12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H12" s="12">
         <f>(VLOOKUP(main!P12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I12" s="12">
         <f>(VLOOKUP(main!Q12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J12" s="12">
         <f>(VLOOKUP(main!R12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K12" s="12">
         <f>(VLOOKUP(main!S12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L12" s="12">
         <f>(VLOOKUP(main!T12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M12" s="12">
         <f>(VLOOKUP(main!U12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N12" s="12">
         <f>(VLOOKUP(main!V12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O12" s="12">
         <f>(VLOOKUP(main!W12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P12" s="12">
         <f>(VLOOKUP(main!X12,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q12" s="12">
         <f>(VLOOKUP(main!Y12,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36434,35 +36656,35 @@
     <row r="13" spans="1:24">
       <c r="A13" s="12">
         <f>(VLOOKUP(main!I13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12">
         <f>(VLOOKUP(main!J13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C13" s="12">
         <f>(VLOOKUP(main!K13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D13" s="12">
         <f>(VLOOKUP(main!L13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E13" s="12">
         <f>(VLOOKUP(main!M13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F13" s="12">
         <f>(VLOOKUP(main!N13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G13" s="12">
         <f>(VLOOKUP(main!O13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H13" s="12">
         <f>(VLOOKUP(main!P13,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I13" s="12">
         <f>(VLOOKUP(main!Q13,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36532,35 +36754,35 @@
     <row r="14" spans="1:24">
       <c r="A14" s="12">
         <f>(VLOOKUP(main!I14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B14" s="12">
         <f>(VLOOKUP(main!J14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C14" s="12">
         <f>(VLOOKUP(main!K14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D14" s="12">
         <f>(VLOOKUP(main!L14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E14" s="12">
         <f>(VLOOKUP(main!M14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F14" s="12">
         <f>(VLOOKUP(main!N14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G14" s="12">
         <f>(VLOOKUP(main!O14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H14" s="12">
         <f>(VLOOKUP(main!P14,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12">
         <f>(VLOOKUP(main!Q14,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36630,35 +36852,35 @@
     <row r="15" spans="1:24">
       <c r="A15" s="12">
         <f>(VLOOKUP(main!I15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B15" s="12">
         <f>(VLOOKUP(main!J15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C15" s="12">
         <f>(VLOOKUP(main!K15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D15" s="12">
         <f>(VLOOKUP(main!L15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E15" s="12">
         <f>(VLOOKUP(main!M15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F15" s="12">
         <f>(VLOOKUP(main!N15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G15" s="12">
         <f>(VLOOKUP(main!O15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H15" s="12">
         <f>(VLOOKUP(main!P15,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I15" s="12">
         <f>(VLOOKUP(main!Q15,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36728,95 +36950,95 @@
     <row r="16" spans="1:24">
       <c r="A16" s="12">
         <f>(VLOOKUP(main!I16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B16" s="12">
         <f>(VLOOKUP(main!J16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C16" s="12">
         <f>(VLOOKUP(main!K16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D16" s="12">
         <f>(VLOOKUP(main!L16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E16" s="12">
         <f>(VLOOKUP(main!M16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F16" s="12">
         <f>(VLOOKUP(main!N16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G16" s="12">
         <f>(VLOOKUP(main!O16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H16" s="12">
         <f>(VLOOKUP(main!P16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12">
         <f>(VLOOKUP(main!Q16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16" s="12">
         <f>(VLOOKUP(main!R16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="K16" s="12">
         <f>(VLOOKUP(main!S16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="L16" s="12">
         <f>(VLOOKUP(main!T16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="M16" s="12">
         <f>(VLOOKUP(main!U16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>44.222109392472198</v>
       </c>
       <c r="N16" s="12">
         <f>(VLOOKUP(main!V16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O16" s="12">
         <f>(VLOOKUP(main!W16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="P16" s="12">
         <f>(VLOOKUP(main!X16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="Q16" s="12">
         <f>(VLOOKUP(main!Y16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="R16" s="12">
         <f>(VLOOKUP(main!Z16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>29.110982162825401</v>
       </c>
       <c r="S16" s="12">
         <f>(VLOOKUP(main!AA16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="T16" s="12">
         <f>(VLOOKUP(main!AB16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="U16" s="12">
         <f>(VLOOKUP(main!AC16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V16" s="12">
         <f>(VLOOKUP(main!AD16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>39.110982162825401</v>
       </c>
       <c r="W16" s="12">
         <f>(VLOOKUP(main!AE16,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X16" s="12">
         <f>(VLOOKUP(main!AF16,main!$AO$4:$AR$55,4,FALSE))</f>
@@ -36826,99 +37048,99 @@
     <row r="17" spans="1:24">
       <c r="A17" s="12">
         <f>(VLOOKUP(main!I17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B17" s="12">
         <f>(VLOOKUP(main!J17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C17" s="12">
         <f>(VLOOKUP(main!K17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D17" s="12">
         <f>(VLOOKUP(main!L17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E17" s="12">
         <f>(VLOOKUP(main!M17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F17" s="12">
         <f>(VLOOKUP(main!N17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G17" s="12">
         <f>(VLOOKUP(main!O17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H17" s="12">
         <f>(VLOOKUP(main!P17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I17" s="12">
         <f>(VLOOKUP(main!Q17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J17" s="12">
         <f>(VLOOKUP(main!R17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K17" s="12">
         <f>(VLOOKUP(main!S17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L17" s="12">
         <f>(VLOOKUP(main!T17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12">
         <f>(VLOOKUP(main!U17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N17" s="12">
         <f>(VLOOKUP(main!V17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O17" s="12">
         <f>(VLOOKUP(main!W17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="P17" s="12">
         <f>(VLOOKUP(main!X17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q17" s="12">
         <f>(VLOOKUP(main!Y17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R17" s="12">
         <f>(VLOOKUP(main!Z17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S17" s="12">
         <f>(VLOOKUP(main!AA17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T17" s="12">
         <f>(VLOOKUP(main!AB17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="U17" s="12">
         <f>(VLOOKUP(main!AC17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V17" s="12">
         <f>(VLOOKUP(main!AD17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W17" s="12">
         <f>(VLOOKUP(main!AE17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X17" s="12">
         <f>(VLOOKUP(main!AF17,main!$AO$4:$AR$55,4,FALSE))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:24">
